--- a/offense.xlsx
+++ b/offense.xlsx
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
         <v>11</v>
@@ -1001,7 +1001,7 @@
         <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
         <v>14</v>
@@ -1010,7 +1010,7 @@
         <v>18</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
         <v>19</v>
@@ -1051,28 +1051,28 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>11</v>
@@ -1107,28 +1107,28 @@
         <v>1</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.9</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.95</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CJ2" t="n">
         <v>0.5454545454545454</v>
@@ -1163,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="DK2" t="n">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="DL2" t="n">
-        <v>5.061855670103093</v>
+        <v>5.05050505050505</v>
       </c>
     </row>
     <row r="3">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" t="n">
         <v>23</v>
@@ -1469,7 +1469,7 @@
         <v>11</v>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
         <v>24</v>
@@ -1478,7 +1478,7 @@
         <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R4" t="n">
         <v>24</v>
@@ -1523,28 +1523,28 @@
         <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB4" t="n">
         <v>31</v>
@@ -1583,28 +1583,28 @@
         <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.325</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.575</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ4" t="n">
         <v>0.4193548387096774</v>
@@ -1643,13 +1643,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ4" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="DK4" t="n">
-        <v>968</v>
+        <v>977</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.407821229050279</v>
+        <v>5.397790055248619</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
@@ -1759,31 +1759,31 @@
         <v>1</v>
       </c>
       <c r="AT5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1815,31 +1815,31 @@
         <v>2</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.5</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CK5" t="n">
         <v>0.5</v>
@@ -1871,13 +1871,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="DK5" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="DL5" t="n">
-        <v>4.872727272727273</v>
+        <v>4.892857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -2162,7 +2162,7 @@
         <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L7" t="n">
         <v>9</v>
@@ -2180,7 +2180,7 @@
         <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
         <v>19</v>
@@ -2223,31 +2223,31 @@
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -2281,31 +2281,31 @@
         <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.225</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.75</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.358974358974359</v>
+        <v>0.375</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.175</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="CK7" t="n">
         <v>0.3333333333333333</v>
@@ -2339,13 +2339,13 @@
         <v>0.25</v>
       </c>
       <c r="DJ7" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="DK7" t="n">
-        <v>792</v>
+        <v>798</v>
       </c>
       <c r="DL7" t="n">
-        <v>5.109677419354838</v>
+        <v>5.115384615384615</v>
       </c>
     </row>
     <row r="8">
@@ -2606,13 +2606,13 @@
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
         <v>7</v>
@@ -2624,7 +2624,7 @@
         <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
         <v>14</v>
@@ -2665,31 +2665,31 @@
         <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2721,31 +2721,31 @@
         <v>2</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.65</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.4</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.15</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.75</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CK9" t="n">
         <v>1</v>
@@ -2777,13 +2777,13 @@
         <v>1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="DK9" t="n">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="DL9" t="n">
-        <v>5.135802469135802</v>
+        <v>5.059523809523809</v>
       </c>
     </row>
     <row r="10">
@@ -2830,13 +2830,13 @@
         <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N10" t="n">
         <v>20</v>
@@ -2848,7 +2848,7 @@
         <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R10" t="n">
         <v>25</v>
@@ -2889,31 +2889,31 @@
         <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
@@ -2945,31 +2945,31 @@
         <v>2</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.825</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.575</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.225</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.9</v>
+        <v>0.9024390243902439</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.85</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="CK10" t="n">
         <v>1</v>
@@ -3001,13 +3001,13 @@
         <v>1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="DK10" t="n">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="DL10" t="n">
-        <v>5.056603773584905</v>
+        <v>5.027906976744186</v>
       </c>
     </row>
     <row r="11">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" t="n">
         <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M12" t="n">
         <v>9</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O12" t="n">
         <v>6</v>
@@ -3304,7 +3304,7 @@
         <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R12" t="n">
         <v>9</v>
@@ -3351,31 +3351,31 @@
         <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>3</v>
@@ -3413,31 +3413,31 @@
         <v>6</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.25</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.65</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CK12" t="n">
         <v>1.333333333333333</v>
@@ -3475,13 +3475,13 @@
         <v>1.166666666666667</v>
       </c>
       <c r="DJ12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="DK12" t="n">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.857142857142857</v>
+        <v>5.747368421052632</v>
       </c>
     </row>
     <row r="13">
@@ -3529,19 +3529,19 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K13" t="n">
         <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" t="n">
         <v>20</v>
       </c>
       <c r="N13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>14</v>
@@ -3550,7 +3550,7 @@
         <v>18</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R13" t="n">
         <v>18</v>
@@ -3597,31 +3597,31 @@
         <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -3659,31 +3659,31 @@
         <v>8</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.5</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="CK13" t="n">
         <v>1.4</v>
@@ -3721,13 +3721,13 @@
         <v>1.25</v>
       </c>
       <c r="DJ13" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="DK13" t="n">
-        <v>913</v>
+        <v>926</v>
       </c>
       <c r="DL13" t="n">
-        <v>5.467065868263473</v>
+        <v>5.415204678362573</v>
       </c>
     </row>
     <row r="14">
@@ -3778,10 +3778,10 @@
         <v>12</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
         <v>1</v>
@@ -3839,31 +3839,31 @@
         <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC14" t="n">
         <v>2</v>
@@ -3897,31 +3897,31 @@
         <v>3</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.45</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.05</v>
+        <v>0.04761904761904762</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CK14" t="n">
         <v>0.5</v>
@@ -3955,13 +3955,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="DJ14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="DK14" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="DL14" t="n">
-        <v>5.315217391304348</v>
+        <v>5.268817204301075</v>
       </c>
     </row>
     <row r="15">
@@ -4240,10 +4240,10 @@
         <v>18</v>
       </c>
       <c r="K16" t="n">
+        <v>22</v>
+      </c>
+      <c r="L16" t="n">
         <v>21</v>
-      </c>
-      <c r="L16" t="n">
-        <v>20</v>
       </c>
       <c r="M16" t="n">
         <v>7</v>
@@ -4301,31 +4301,31 @@
         <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC16" t="n">
         <v>4</v>
@@ -4359,31 +4359,31 @@
         <v>5</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.525</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.1794871794871795</v>
+        <v>0.175</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.375</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.675</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.4</v>
       </c>
       <c r="CK16" t="n">
         <v>1.25</v>
@@ -4417,13 +4417,13 @@
         <v>1.2</v>
       </c>
       <c r="DJ16" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="DK16" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="DL16" t="n">
-        <v>5.380368098159509</v>
+        <v>5.353658536585366</v>
       </c>
     </row>
     <row r="17">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
@@ -4494,7 +4494,7 @@
         <v>10</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T17" t="n">
         <v>8</v>
@@ -4529,28 +4529,28 @@
         <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -4585,28 +4585,28 @@
         <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CJ17" t="n">
         <v>0.7272727272727273</v>
@@ -4641,13 +4641,13 @@
         <v>1.25</v>
       </c>
       <c r="DJ17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="DK17" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="DL17" t="n">
-        <v>5.585714285714285</v>
+        <v>5.652777777777778</v>
       </c>
     </row>
     <row r="18">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K19" t="n">
         <v>21</v>
@@ -4948,7 +4948,7 @@
         <v>25</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
         <v>15</v>
@@ -4985,28 +4985,28 @@
         <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA19" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB19" t="n">
         <v>33</v>
@@ -5043,28 +5043,28 @@
         <v>6</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.575</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.625</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.717948717948718</v>
+        <v>0.7</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.25</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.282051282051282</v>
+        <v>0.275</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.625</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.282051282051282</v>
+        <v>0.325</v>
       </c>
       <c r="CJ19" t="n">
         <v>0.4545454545454545</v>
@@ -5101,13 +5101,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ19" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="DK19" t="n">
-        <v>785</v>
+        <v>801</v>
       </c>
       <c r="DL19" t="n">
-        <v>4.644970414201183</v>
+        <v>4.684210526315789</v>
       </c>
     </row>
     <row r="20">
@@ -5158,7 +5158,7 @@
         <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
         <v>11</v>
@@ -5167,22 +5167,22 @@
         <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
         <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -5219,31 +5219,31 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC20" t="n">
         <v>1</v>
@@ -5277,31 +5277,31 @@
         <v>2</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.055555555555556</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="CJ20" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
@@ -5335,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="DK20" t="n">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="DL20" t="n">
-        <v>5.272727272727272</v>
+        <v>5.285714285714286</v>
       </c>
     </row>
     <row r="21">
@@ -5620,7 +5620,7 @@
         <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" t="n">
         <v>25</v>
@@ -5629,22 +5629,22 @@
         <v>7</v>
       </c>
       <c r="N22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R22" t="n">
         <v>26</v>
       </c>
       <c r="S22" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T22" t="n">
         <v>9</v>
@@ -5681,31 +5681,31 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AU22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AV22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AW22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AX22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AY22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BA22" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC22" t="n">
         <v>3</v>
@@ -5739,31 +5739,31 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CG22" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.8536585365853658</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CJ22" t="n">
-        <v>0.28125</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CK22" t="n">
         <v>1</v>
@@ -5797,13 +5797,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ22" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="DK22" t="n">
-        <v>909</v>
+        <v>931</v>
       </c>
       <c r="DL22" t="n">
-        <v>5.378698224852071</v>
+        <v>5.381502890173411</v>
       </c>
     </row>
     <row r="23">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
         <v>16</v>
@@ -6078,7 +6078,7 @@
         <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
         <v>12</v>
@@ -6090,10 +6090,10 @@
         <v>6</v>
       </c>
       <c r="Q24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S24" t="n">
         <v>12</v>
@@ -6131,31 +6131,31 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>1</v>
@@ -6187,31 +6187,31 @@
         <v>1</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CK24" t="n">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>0</v>
       </c>
       <c r="DJ24" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="DK24" t="n">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="DL24" t="n">
-        <v>5.357142857142857</v>
+        <v>5.277777777777778</v>
       </c>
     </row>
     <row r="25">
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
         <v>22</v>
@@ -6306,7 +6306,7 @@
         <v>21</v>
       </c>
       <c r="M25" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N25" t="n">
         <v>18</v>
@@ -6318,10 +6318,10 @@
         <v>19</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S25" t="n">
         <v>21</v>
@@ -6359,31 +6359,31 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA25" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB25" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC25" t="n">
         <v>1</v>
@@ -6415,31 +6415,31 @@
         <v>1</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.275</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.45</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.55</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="CK25" t="n">
         <v>0</v>
@@ -6471,13 +6471,13 @@
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="DK25" t="n">
-        <v>813</v>
+        <v>838</v>
       </c>
       <c r="DL25" t="n">
-        <v>5.145569620253164</v>
+        <v>5.109756097560975</v>
       </c>
     </row>
     <row r="26">
@@ -6524,7 +6524,7 @@
         <v>13</v>
       </c>
       <c r="K26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
         <v>6</v>
@@ -6533,10 +6533,10 @@
         <v>12</v>
       </c>
       <c r="N26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P26" t="n">
         <v>4</v>
@@ -6587,31 +6587,31 @@
         <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
         <v>2</v>
@@ -6647,31 +6647,31 @@
         <v>4</v>
       </c>
       <c r="CB26" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CC26" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CD26" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CE26" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="CF26" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CG26" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="CH26" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CI26" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CJ26" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CK26" t="n">
         <v>1.5</v>
@@ -6707,13 +6707,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ26" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="DK26" t="n">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="DL26" t="n">
-        <v>5.469026548672566</v>
+        <v>5.413793103448276</v>
       </c>
     </row>
     <row r="27">
@@ -6984,7 +6984,7 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" t="n">
         <v>12</v>
@@ -6993,10 +6993,10 @@
         <v>15</v>
       </c>
       <c r="N28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P28" t="n">
         <v>7</v>
@@ -7047,31 +7047,31 @@
         <v>11</v>
       </c>
       <c r="AT28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -7107,31 +7107,31 @@
         <v>6</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.3</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.275</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.675</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.175</v>
+        <v>0.1707317073170732</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="CK28" t="n">
         <v>1.75</v>
@@ -7167,13 +7167,13 @@
         <v>1.833333333333333</v>
       </c>
       <c r="DJ28" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="DK28" t="n">
-        <v>925</v>
+        <v>935</v>
       </c>
       <c r="DL28" t="n">
-        <v>5.572289156626506</v>
+        <v>5.532544378698224</v>
       </c>
     </row>
     <row r="29">
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K30" t="n">
         <v>13</v>
@@ -7461,13 +7461,13 @@
         <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q30" t="n">
         <v>6</v>
@@ -7513,31 +7513,31 @@
         <v>1</v>
       </c>
       <c r="AT30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC30" t="n">
         <v>1</v>
@@ -7571,31 +7571,31 @@
         <v>2</v>
       </c>
       <c r="CB30" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CC30" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CD30" t="n">
-        <v>0.65</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CE30" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CF30" t="n">
-        <v>0.3</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CG30" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CH30" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CI30" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CJ30" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CK30" t="n">
         <v>0</v>
@@ -7629,13 +7629,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ30" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="DK30" t="n">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="DL30" t="n">
-        <v>5.348314606741573</v>
+        <v>5.308510638297872</v>
       </c>
     </row>
     <row r="31">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
         <v>23</v>
@@ -7695,13 +7695,13 @@
         <v>25</v>
       </c>
       <c r="N31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O31" t="n">
         <v>24</v>
       </c>
       <c r="P31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q31" t="n">
         <v>11</v>
@@ -7747,31 +7747,31 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC31" t="n">
         <v>3</v>
@@ -7805,31 +7805,31 @@
         <v>4</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.65</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.475</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.575</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.6</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="CK31" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0.25</v>
       </c>
       <c r="DJ31" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="DK31" t="n">
-        <v>904</v>
+        <v>927</v>
       </c>
       <c r="DL31" t="n">
-        <v>4.783068783068783</v>
+        <v>4.778350515463917</v>
       </c>
     </row>
     <row r="32">
@@ -8154,13 +8154,13 @@
         <v>13</v>
       </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L33" t="n">
         <v>13</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N33" t="n">
         <v>20</v>
@@ -8215,31 +8215,31 @@
         <v>1</v>
       </c>
       <c r="AT33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC33" t="n">
         <v>1</v>
@@ -8273,31 +8273,31 @@
         <v>2</v>
       </c>
       <c r="CB33" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CC33" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="CD33" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="CE33" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CF33" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CG33" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CH33" t="n">
-        <v>0.391304347826087</v>
+        <v>0.375</v>
       </c>
       <c r="CI33" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CJ33" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CK33" t="n">
         <v>1</v>
@@ -8331,13 +8331,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ33" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="DK33" t="n">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="DL33" t="n">
-        <v>4.76595744680851</v>
+        <v>4.736842105263158</v>
       </c>
     </row>
     <row r="34">
@@ -8388,13 +8388,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L34" t="n">
         <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N34" t="n">
         <v>26</v>
@@ -8449,31 +8449,31 @@
         <v>5</v>
       </c>
       <c r="AT34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA34" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC34" t="n">
         <v>4</v>
@@ -8507,31 +8507,31 @@
         <v>6</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CC34" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.45</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CE34" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CF34" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.675</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="CK34" t="n">
         <v>1</v>
@@ -8565,13 +8565,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ34" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="DK34" t="n">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="DL34" t="n">
-        <v>4.822857142857143</v>
+        <v>4.806818181818182</v>
       </c>
     </row>
     <row r="35">
@@ -8850,7 +8850,7 @@
         <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L36" t="n">
         <v>14</v>
@@ -8909,31 +8909,31 @@
         <v>3</v>
       </c>
       <c r="AT36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC36" t="n">
         <v>2</v>
@@ -8965,31 +8965,31 @@
         <v>2</v>
       </c>
       <c r="CB36" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CC36" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5</v>
       </c>
       <c r="CD36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CE36" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CF36" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CG36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CH36" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CI36" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CJ36" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CK36" t="n">
         <v>1.5</v>
@@ -9078,7 +9078,7 @@
         <v>16</v>
       </c>
       <c r="K37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L37" t="n">
         <v>30</v>
@@ -9137,31 +9137,31 @@
         <v>4</v>
       </c>
       <c r="AT37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA37" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB37" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
         <v>3</v>
@@ -9193,31 +9193,31 @@
         <v>3</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.75</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="CC37" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CD37" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CE37" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CF37" t="n">
-        <v>0.8</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CG37" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.40625</v>
       </c>
       <c r="CK37" t="n">
         <v>1.333333333333333</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
         <v>15</v>
@@ -9555,10 +9555,10 @@
         <v>19</v>
       </c>
       <c r="P39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R39" t="n">
         <v>12</v>
@@ -9567,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
@@ -9599,31 +9599,31 @@
         <v>1</v>
       </c>
       <c r="AT39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC39" t="n">
         <v>2</v>
@@ -9655,31 +9655,31 @@
         <v>2</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="CF39" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CK39" t="n">
         <v>0.5</v>
@@ -9711,13 +9711,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ39" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="DK39" t="n">
-        <v>558</v>
+        <v>593</v>
       </c>
       <c r="DL39" t="n">
-        <v>5.072727272727272</v>
+        <v>5.112068965517241</v>
       </c>
     </row>
     <row r="40">
@@ -9765,7 +9765,7 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K40" t="n">
         <v>25</v>
@@ -9783,10 +9783,10 @@
         <v>32</v>
       </c>
       <c r="P40" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R40" t="n">
         <v>17</v>
@@ -9795,7 +9795,7 @@
         <v>18</v>
       </c>
       <c r="T40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U40" t="n">
         <v>4</v>
@@ -9829,31 +9829,31 @@
         <v>5</v>
       </c>
       <c r="AT40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB40" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC40" t="n">
         <v>5</v>
@@ -9887,31 +9887,31 @@
         <v>6</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.6</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.3</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.8</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.425</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CG40" t="n">
-        <v>0.35</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="CK40" t="n">
         <v>0.8</v>
@@ -9945,13 +9945,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ40" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="DK40" t="n">
-        <v>805</v>
+        <v>840</v>
       </c>
       <c r="DL40" t="n">
-        <v>4.707602339181286</v>
+        <v>4.745762711864407</v>
       </c>
     </row>
     <row r="41">
@@ -10230,10 +10230,10 @@
         <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
         <v>9</v>
@@ -10291,31 +10291,31 @@
         <v>4</v>
       </c>
       <c r="AT42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB42" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC42" t="n">
         <v>2</v>
@@ -10349,31 +10349,31 @@
         <v>3</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CC42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="CD42" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CE42" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="CG42" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CH42" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="CK42" t="n">
         <v>2</v>
@@ -10407,13 +10407,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ42" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="DK42" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="DL42" t="n">
-        <v>5.661764705882353</v>
+        <v>5.594202898550725</v>
       </c>
     </row>
     <row r="43">
@@ -10464,10 +10464,10 @@
         <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L43" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M43" t="n">
         <v>16</v>
@@ -10525,31 +10525,31 @@
         <v>6</v>
       </c>
       <c r="AT43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA43" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB43" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC43" t="n">
         <v>4</v>
@@ -10583,31 +10583,31 @@
         <v>5</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.55</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CE43" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CF43" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CG43" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.46875</v>
       </c>
       <c r="CK43" t="n">
         <v>1.5</v>
@@ -10641,13 +10641,13 @@
         <v>1.2</v>
       </c>
       <c r="DJ43" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="DK43" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="DL43" t="n">
-        <v>5.042168674698795</v>
+        <v>5.017964071856287</v>
       </c>
     </row>
     <row r="44">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K44" t="n">
         <v>9</v>
@@ -10710,7 +10710,7 @@
         <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
         <v>13</v>
@@ -10722,7 +10722,7 @@
         <v>4</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T44" t="n">
         <v>3</v>
@@ -10753,28 +10753,28 @@
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB44" t="n">
         <v>9</v>
@@ -10807,28 +10807,28 @@
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="CC44" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CE44" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CF44" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="CH44" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="CJ44" t="n">
         <v>0.3333333333333333</v>
@@ -10859,13 +10859,13 @@
       <c r="DH44" t="inlineStr"/>
       <c r="DI44" t="inlineStr"/>
       <c r="DJ44" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="DK44" t="n">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="DL44" t="n">
-        <v>4.74468085106383</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="45">
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
         <v>21</v>
@@ -11156,7 +11156,7 @@
         <v>26</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
         <v>18</v>
@@ -11168,7 +11168,7 @@
         <v>15</v>
       </c>
       <c r="S46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T46" t="n">
         <v>20</v>
@@ -11203,28 +11203,28 @@
         <v>2</v>
       </c>
       <c r="AT46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA46" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB46" t="n">
         <v>31</v>
@@ -11259,28 +11259,28 @@
         <v>1</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.358974358974359</v>
+        <v>0.35</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.282051282051282</v>
+        <v>0.275</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.375</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="CJ46" t="n">
         <v>0.6451612903225806</v>
@@ -11315,13 +11315,13 @@
         <v>2</v>
       </c>
       <c r="DJ46" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="DK46" t="n">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="DL46" t="n">
-        <v>5.102739726027397</v>
+        <v>5.134228187919463</v>
       </c>
     </row>
     <row r="47">
@@ -11597,7 +11597,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" t="n">
         <v>7</v>
@@ -11606,7 +11606,7 @@
         <v>11</v>
       </c>
       <c r="M48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="N48" t="n">
         <v>11</v>
@@ -11624,10 +11624,10 @@
         <v>6</v>
       </c>
       <c r="S48" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T48" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -11659,31 +11659,31 @@
         <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
         <v>1</v>
@@ -11715,31 +11715,31 @@
         <v>1</v>
       </c>
       <c r="CB48" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CC48" t="n">
-        <v>0.9090909090909091</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="CD48" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CE48" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="CF48" t="n">
-        <v>1</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="CG48" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CH48" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CI48" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CJ48" t="n">
-        <v>1</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="CK48" t="n">
         <v>0</v>
@@ -11771,13 +11771,13 @@
         <v>0</v>
       </c>
       <c r="DJ48" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="DK48" t="n">
-        <v>648</v>
+        <v>682</v>
       </c>
       <c r="DL48" t="n">
-        <v>4.984615384615385</v>
+        <v>4.978102189781022</v>
       </c>
     </row>
     <row r="49">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
         <v>13</v>
@@ -11834,7 +11834,7 @@
         <v>21</v>
       </c>
       <c r="M49" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N49" t="n">
         <v>20</v>
@@ -11852,10 +11852,10 @@
         <v>14</v>
       </c>
       <c r="S49" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T49" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="U49" t="n">
         <v>1</v>
@@ -11887,31 +11887,31 @@
         <v>1</v>
       </c>
       <c r="AT49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA49" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB49" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC49" t="n">
         <v>2</v>
@@ -11943,31 +11943,31 @@
         <v>2</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.525</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.8</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.55</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CJ49" t="n">
-        <v>1</v>
+        <v>1.032258064516129</v>
       </c>
       <c r="CK49" t="n">
         <v>0.5</v>
@@ -11999,13 +11999,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ49" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="DK49" t="n">
-        <v>1101</v>
+        <v>1135</v>
       </c>
       <c r="DL49" t="n">
-        <v>4.981900452488688</v>
+        <v>4.978070175438597</v>
       </c>
     </row>
     <row r="50">
@@ -12053,7 +12053,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
         <v>12</v>
@@ -12065,7 +12065,7 @@
         <v>12</v>
       </c>
       <c r="N50" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O50" t="n">
         <v>16</v>
@@ -12080,7 +12080,7 @@
         <v>10</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="T50" t="n">
         <v>5</v>
@@ -12115,28 +12115,28 @@
         <v>2</v>
       </c>
       <c r="AT50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA50" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB50" t="n">
         <v>14</v>
@@ -12171,28 +12171,28 @@
         <v>2</v>
       </c>
       <c r="CB50" t="n">
-        <v>0.84</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="CC50" t="n">
-        <v>0.48</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CD50" t="n">
-        <v>0.36</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="CE50" t="n">
-        <v>0.64</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CF50" t="n">
-        <v>0.24</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="CG50" t="n">
-        <v>0.4</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CH50" t="n">
-        <v>0.4</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="CI50" t="n">
-        <v>0.8</v>
+        <v>0.8846153846153846</v>
       </c>
       <c r="CJ50" t="n">
         <v>0.3571428571428572</v>
@@ -12227,13 +12227,13 @@
         <v>1</v>
       </c>
       <c r="DJ50" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="DK50" t="n">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="DL50" t="n">
-        <v>4.693693693693693</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="51">
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
         <v>22</v>
@@ -12511,7 +12511,7 @@
         <v>22</v>
       </c>
       <c r="N52" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O52" t="n">
         <v>26</v>
@@ -12526,7 +12526,7 @@
         <v>11</v>
       </c>
       <c r="S52" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="T52" t="n">
         <v>8</v>
@@ -12561,28 +12561,28 @@
         <v>2</v>
       </c>
       <c r="AT52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA52" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB52" t="n">
         <v>29</v>
@@ -12617,28 +12617,28 @@
         <v>2</v>
       </c>
       <c r="CB52" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.275</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CE52" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CF52" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.8</v>
+        <v>0.8536585365853658</v>
       </c>
       <c r="CJ52" t="n">
         <v>0.2758620689655172</v>
@@ -12673,13 +12673,13 @@
         <v>1</v>
       </c>
       <c r="DJ52" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="DK52" t="n">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="DL52" t="n">
-        <v>4.678362573099415</v>
+        <v>4.715909090909091</v>
       </c>
     </row>
     <row r="53">
@@ -12956,7 +12956,7 @@
         <v>9</v>
       </c>
       <c r="K54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L54" t="n">
         <v>6</v>
@@ -12974,7 +12974,7 @@
         <v>8</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R54" t="n">
         <v>7</v>
@@ -13017,31 +13017,31 @@
         <v>2</v>
       </c>
       <c r="AT54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB54" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC54" t="n">
         <v>4</v>
@@ -13075,31 +13075,31 @@
         <v>5</v>
       </c>
       <c r="CB54" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CC54" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CD54" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="CE54" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CF54" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CG54" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CH54" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CI54" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CJ54" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CK54" t="n">
         <v>0.5</v>
@@ -13133,13 +13133,13 @@
         <v>0.4</v>
       </c>
       <c r="DJ54" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="DK54" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="DL54" t="n">
-        <v>5.164383561643835</v>
+        <v>5.175675675675675</v>
       </c>
     </row>
     <row r="55">
@@ -13186,7 +13186,7 @@
         <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L55" t="n">
         <v>19</v>
@@ -13204,7 +13204,7 @@
         <v>16</v>
       </c>
       <c r="Q55" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R55" t="n">
         <v>8</v>
@@ -13247,31 +13247,31 @@
         <v>8</v>
       </c>
       <c r="AT55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA55" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB55" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BC55" t="n">
         <v>7</v>
@@ -13305,31 +13305,31 @@
         <v>9</v>
       </c>
       <c r="CB55" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CC55" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CD55" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2</v>
       </c>
       <c r="CE55" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CF55" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CG55" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.525</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="CK55" t="n">
         <v>0.7142857142857143</v>
@@ -13363,13 +13363,13 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="DJ55" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="DK55" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="DL55" t="n">
-        <v>4.876811594202898</v>
+        <v>4.884892086330935</v>
       </c>
     </row>
     <row r="56">
@@ -13413,16 +13413,16 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
         <v>12</v>
       </c>
       <c r="L56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N56" t="n">
         <v>13</v>
@@ -13434,7 +13434,7 @@
         <v>15</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R56" t="n">
         <v>7</v>
@@ -13477,28 +13477,28 @@
         <v>3</v>
       </c>
       <c r="AT56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA56" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB56" t="n">
         <v>15</v>
@@ -13535,28 +13535,28 @@
         <v>5</v>
       </c>
       <c r="CB56" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CC56" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD56" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CE56" t="n">
-        <v>0.1739130434782609</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CF56" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.625</v>
       </c>
       <c r="CG56" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CH56" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="CI56" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="CJ56" t="n">
         <v>0.6</v>
@@ -13593,13 +13593,13 @@
         <v>0.6</v>
       </c>
       <c r="DJ56" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="DK56" t="n">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="DL56" t="n">
-        <v>5.346153846153846</v>
+        <v>5.181818181818182</v>
       </c>
     </row>
     <row r="57">
@@ -13867,16 +13867,16 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
         <v>22</v>
       </c>
       <c r="L58" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M58" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N58" t="n">
         <v>18</v>
@@ -13888,7 +13888,7 @@
         <v>21</v>
       </c>
       <c r="Q58" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R58" t="n">
         <v>18</v>
@@ -13931,28 +13931,28 @@
         <v>7</v>
       </c>
       <c r="AT58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA58" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB58" t="n">
         <v>32</v>
@@ -13989,28 +13989,28 @@
         <v>7</v>
       </c>
       <c r="CB58" t="n">
-        <v>0.725</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="CC58" t="n">
-        <v>0.25</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="CD58" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CE58" t="n">
-        <v>0.225</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="CF58" t="n">
-        <v>0.525</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CG58" t="n">
-        <v>0.4</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CH58" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CJ58" t="n">
         <v>0.34375</v>
@@ -14047,13 +14047,13 @@
         <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="DK58" t="n">
-        <v>835</v>
+        <v>849</v>
       </c>
       <c r="DL58" t="n">
-        <v>5.091463414634147</v>
+        <v>4.994117647058824</v>
       </c>
     </row>
     <row r="59">
@@ -14344,7 +14344,7 @@
         <v>13</v>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L60" t="n">
         <v>21</v>
@@ -14356,10 +14356,10 @@
         <v>5</v>
       </c>
       <c r="O60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q60" t="n">
         <v>8</v>
@@ -14403,31 +14403,31 @@
         <v>7</v>
       </c>
       <c r="AT60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB60" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC60" t="n">
         <v>4</v>
@@ -14459,31 +14459,31 @@
         <v>4</v>
       </c>
       <c r="CB60" t="n">
-        <v>1</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="CC60" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CD60" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="CF60" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CH60" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CK60" t="n">
         <v>1.75</v>
@@ -14515,13 +14515,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ60" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="DK60" t="n">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="DL60" t="n">
-        <v>5.252173913043478</v>
+        <v>5.239316239316239</v>
       </c>
     </row>
     <row r="61">
@@ -14572,7 +14572,7 @@
         <v>19</v>
       </c>
       <c r="K61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L61" t="n">
         <v>39</v>
@@ -14584,10 +14584,10 @@
         <v>14</v>
       </c>
       <c r="O61" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Q61" t="n">
         <v>17</v>
@@ -14635,31 +14635,31 @@
         <v>8</v>
       </c>
       <c r="AT61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA61" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB61" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC61" t="n">
         <v>6</v>
@@ -14695,31 +14695,31 @@
         <v>8</v>
       </c>
       <c r="CB61" t="n">
-        <v>0.975</v>
+        <v>0.9512195121951219</v>
       </c>
       <c r="CC61" t="n">
-        <v>0.275</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="CD61" t="n">
-        <v>0.35</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="CE61" t="n">
-        <v>0.75</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="CF61" t="n">
-        <v>0.575</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="CG61" t="n">
-        <v>0.425</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CI61" t="n">
-        <v>0.675</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.5</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="CK61" t="n">
         <v>1.333333333333333</v>
@@ -14755,13 +14755,13 @@
         <v>1</v>
       </c>
       <c r="DJ61" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="DK61" t="n">
-        <v>1092</v>
+        <v>1101</v>
       </c>
       <c r="DL61" t="n">
-        <v>5.079069767441861</v>
+        <v>5.073732718894009</v>
       </c>
     </row>
     <row r="62">
@@ -15046,7 +15046,7 @@
         <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -15101,31 +15101,31 @@
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB63" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="CC63" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="CD63" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="CE63" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="CF63" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5</v>
       </c>
       <c r="CG63" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="CH63" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CI63" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CK63" t="inlineStr"/>
       <c r="CL63" t="inlineStr"/>
@@ -15264,7 +15264,7 @@
         <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L64" t="n">
         <v>15</v>
@@ -15325,31 +15325,31 @@
         <v>4</v>
       </c>
       <c r="AT64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA64" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB64" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC64" t="n">
         <v>5</v>
@@ -15383,31 +15383,31 @@
         <v>6</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CC64" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.85</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="CE64" t="n">
-        <v>0.7</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="CF64" t="n">
-        <v>0.45</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CG64" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CH64" t="n">
-        <v>0.65</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="CI64" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="CK64" t="n">
         <v>0.8</v>
@@ -15495,7 +15495,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K65" t="n">
         <v>9</v>
@@ -15510,13 +15510,13 @@
         <v>4</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P65" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q65" t="n">
         <v>10</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>9</v>
       </c>
       <c r="R65" t="n">
         <v>4</v>
@@ -15559,28 +15559,28 @@
         <v>1</v>
       </c>
       <c r="AT65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA65" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB65" t="n">
         <v>11</v>
@@ -15617,28 +15617,28 @@
         <v>2</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CC65" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CE65" t="n">
-        <v>0.3</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.5</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CG65" t="n">
-        <v>0.45</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CH65" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CI65" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CJ65" t="n">
         <v>0.6363636363636364</v>
@@ -15675,13 +15675,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ65" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="DK65" t="n">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="DL65" t="n">
-        <v>4.802469135802469</v>
+        <v>4.790697674418604</v>
       </c>
     </row>
     <row r="66">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K67" t="n">
         <v>19</v>
@@ -15972,13 +15972,13 @@
         <v>6</v>
       </c>
       <c r="O67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P67" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q67" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R67" t="n">
         <v>8</v>
@@ -16021,28 +16021,28 @@
         <v>8</v>
       </c>
       <c r="AT67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA67" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB67" t="n">
         <v>31</v>
@@ -16079,28 +16079,28 @@
         <v>6</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.725</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.375</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="CD67" t="n">
-        <v>0.15</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="CE67" t="n">
-        <v>0.35</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CF67" t="n">
-        <v>0.425</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="CG67" t="n">
-        <v>0.525</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.2</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ67" t="n">
         <v>0.6774193548387096</v>
@@ -16137,13 +16137,13 @@
         <v>1.333333333333333</v>
       </c>
       <c r="DJ67" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="DK67" t="n">
-        <v>830</v>
+        <v>853</v>
       </c>
       <c r="DL67" t="n">
-        <v>5.220125786163522</v>
+        <v>5.201219512195122</v>
       </c>
     </row>
     <row r="68">
@@ -16191,7 +16191,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K68" t="n">
         <v>8</v>
@@ -16206,7 +16206,7 @@
         <v>8</v>
       </c>
       <c r="O68" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P68" t="n">
         <v>8</v>
@@ -16221,7 +16221,7 @@
         <v>17</v>
       </c>
       <c r="T68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U68" t="n">
         <v>3</v>
@@ -16253,31 +16253,31 @@
         <v>3</v>
       </c>
       <c r="AT68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA68" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC68" t="n">
         <v>3</v>
@@ -16309,31 +16309,31 @@
         <v>3</v>
       </c>
       <c r="CB68" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CD68" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="CE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF68" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="CG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH68" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CI68" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CJ68" t="n">
         <v>0.4</v>
-      </c>
-      <c r="CE68" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CF68" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CG68" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="CH68" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="CI68" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="CJ68" t="n">
-        <v>0.3333333333333333</v>
       </c>
       <c r="CK68" t="n">
         <v>1</v>
@@ -16365,13 +16365,13 @@
         <v>1</v>
       </c>
       <c r="DJ68" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="DK68" t="n">
-        <v>571</v>
+        <v>592</v>
       </c>
       <c r="DL68" t="n">
-        <v>5.098214285714286</v>
+        <v>5.103448275862069</v>
       </c>
     </row>
     <row r="69">
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
         <v>16</v>
@@ -16662,7 +16662,7 @@
         <v>15</v>
       </c>
       <c r="O70" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P70" t="n">
         <v>15</v>
@@ -16677,7 +16677,7 @@
         <v>32</v>
       </c>
       <c r="T70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U70" t="n">
         <v>6</v>
@@ -16709,31 +16709,31 @@
         <v>6</v>
       </c>
       <c r="AT70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AU70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AV70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AW70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AX70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AY70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AZ70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BA70" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BB70" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC70" t="n">
         <v>4</v>
@@ -16765,31 +16765,31 @@
         <v>4</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="CC70" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.3421052631578947</v>
       </c>
       <c r="CD70" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="CE70" t="n">
-        <v>0.7567567567567568</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="CF70" t="n">
-        <v>0.4054054054054054</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="CG70" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="CH70" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="CK70" t="n">
         <v>1.5</v>
@@ -16821,13 +16821,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ70" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="DK70" t="n">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="DL70" t="n">
-        <v>5.193717277486911</v>
+        <v>5.194871794871795</v>
       </c>
     </row>
     <row r="71">
@@ -17116,13 +17116,13 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N72" t="n">
         <v>5</v>
@@ -17131,10 +17131,10 @@
         <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R72" t="n">
         <v>8</v>
@@ -17146,12 +17146,14 @@
         <v>16</v>
       </c>
       <c r="U72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V72" t="n">
         <v>2</v>
       </c>
-      <c r="W72" t="inlineStr"/>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
@@ -17174,42 +17176,44 @@
       <c r="AQ72" t="inlineStr"/>
       <c r="AR72" t="inlineStr"/>
       <c r="AS72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB72" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD72" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE72" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>1</v>
+      </c>
       <c r="BF72" t="inlineStr"/>
       <c r="BG72" t="inlineStr"/>
       <c r="BH72" t="inlineStr"/>
@@ -17232,42 +17236,44 @@
       <c r="BY72" t="inlineStr"/>
       <c r="BZ72" t="inlineStr"/>
       <c r="CA72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CB72" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CC72" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CD72" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CE72" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CF72" t="n">
-        <v>0.55</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CG72" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CH72" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CI72" t="n">
-        <v>0.1</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.8</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="CL72" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM72" t="inlineStr"/>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CM72" t="n">
+        <v>0</v>
+      </c>
       <c r="CN72" t="inlineStr"/>
       <c r="CO72" t="inlineStr"/>
       <c r="CP72" t="inlineStr"/>
@@ -17290,16 +17296,16 @@
       <c r="DG72" t="inlineStr"/>
       <c r="DH72" t="inlineStr"/>
       <c r="DI72" t="n">
-        <v>1.333333333333333</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="DJ72" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="DK72" t="n">
-        <v>459</v>
+        <v>493</v>
       </c>
       <c r="DL72" t="n">
-        <v>5.530120481927711</v>
+        <v>5.53932584269663</v>
       </c>
     </row>
     <row r="73">
@@ -17346,13 +17352,13 @@
         <v>22</v>
       </c>
       <c r="K73" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L73" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M73" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N73" t="n">
         <v>8</v>
@@ -17361,10 +17367,10 @@
         <v>16</v>
       </c>
       <c r="P73" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q73" t="n">
         <v>29</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>28</v>
       </c>
       <c r="R73" t="n">
         <v>13</v>
@@ -17376,7 +17382,7 @@
         <v>20</v>
       </c>
       <c r="U73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V73" t="n">
         <v>3</v>
@@ -17408,43 +17414,43 @@
       <c r="AQ73" t="inlineStr"/>
       <c r="AR73" t="inlineStr"/>
       <c r="AS73" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA73" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB73" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC73" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BE73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF73" t="n">
         <v>1</v>
@@ -17470,40 +17476,40 @@
       <c r="BY73" t="inlineStr"/>
       <c r="BZ73" t="inlineStr"/>
       <c r="CA73" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.65</v>
+        <v>0.6585365853658537</v>
       </c>
       <c r="CC73" t="n">
+        <v>0.7560975609756098</v>
+      </c>
+      <c r="CD73" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="CE73" t="n">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="CF73" t="n">
+        <v>0.7317073170731707</v>
+      </c>
+      <c r="CG73" t="n">
+        <v>0.7073170731707317</v>
+      </c>
+      <c r="CH73" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="CI73" t="n">
+        <v>0.4878048780487805</v>
+      </c>
+      <c r="CJ73" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="CK73" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="CL73" t="n">
         <v>0.75</v>
-      </c>
-      <c r="CD73" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="CE73" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="CF73" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="CG73" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="CH73" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="CI73" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="CJ73" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CK73" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL73" t="n">
-        <v>1</v>
       </c>
       <c r="CM73" t="n">
         <v>0</v>
@@ -17532,16 +17538,16 @@
       <c r="DG73" t="inlineStr"/>
       <c r="DH73" t="inlineStr"/>
       <c r="DI73" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="DJ73" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="DK73" t="n">
-        <v>1024</v>
+        <v>1058</v>
       </c>
       <c r="DL73" t="n">
-        <v>5.12</v>
+        <v>5.135922330097087</v>
       </c>
     </row>
     <row r="74">
@@ -17826,7 +17832,7 @@
         <v>13</v>
       </c>
       <c r="K75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L75" t="n">
         <v>9</v>
@@ -17838,7 +17844,7 @@
         <v>9</v>
       </c>
       <c r="O75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P75" t="n">
         <v>23</v>
@@ -17885,34 +17891,34 @@
         <v>5</v>
       </c>
       <c r="AT75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD75" t="inlineStr"/>
       <c r="BE75" t="inlineStr"/>
@@ -17938,37 +17944,37 @@
       <c r="BY75" t="inlineStr"/>
       <c r="BZ75" t="inlineStr"/>
       <c r="CA75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.5</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CC75" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CD75" t="n">
-        <v>0.5</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="CE75" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CF75" t="n">
-        <v>1.277777777777778</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="CG75" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="CH75" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="CI75" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="CK75" t="n">
-        <v>2.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="CL75" t="inlineStr"/>
       <c r="CM75" t="inlineStr"/>
@@ -17994,16 +18000,16 @@
       <c r="DG75" t="inlineStr"/>
       <c r="DH75" t="inlineStr"/>
       <c r="DI75" t="n">
-        <v>2.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="DJ75" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="DK75" t="n">
-        <v>547</v>
+        <v>555</v>
       </c>
       <c r="DL75" t="n">
-        <v>5.697916666666667</v>
+        <v>5.663265306122449</v>
       </c>
     </row>
     <row r="76">
@@ -18054,7 +18060,7 @@
         <v>23</v>
       </c>
       <c r="K76" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L76" t="n">
         <v>19</v>
@@ -18066,7 +18072,7 @@
         <v>23</v>
       </c>
       <c r="O76" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P76" t="n">
         <v>25</v>
@@ -18115,34 +18121,34 @@
         <v>9</v>
       </c>
       <c r="AT76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA76" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB76" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD76" t="n">
         <v>1</v>
@@ -18170,37 +18176,37 @@
       <c r="BY76" t="inlineStr"/>
       <c r="BZ76" t="inlineStr"/>
       <c r="CA76" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.5</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CC76" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2051282051282051</v>
       </c>
       <c r="CD76" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.5897435897435898</v>
       </c>
       <c r="CE76" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.4102564102564102</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="CG76" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="CH76" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3125</v>
       </c>
       <c r="CK76" t="n">
-        <v>1.6</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="CL76" t="n">
         <v>1</v>
@@ -18228,16 +18234,16 @@
       <c r="DG76" t="inlineStr"/>
       <c r="DH76" t="inlineStr"/>
       <c r="DI76" t="n">
-        <v>1.5</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="DJ76" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="DK76" t="n">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="DL76" t="n">
-        <v>5.426966292134831</v>
+        <v>5.411111111111111</v>
       </c>
     </row>
     <row r="77">
@@ -18281,7 +18287,7 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K77" t="n">
         <v>9</v>
@@ -18290,7 +18296,7 @@
         <v>9</v>
       </c>
       <c r="M77" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N77" t="n">
         <v>6</v>
@@ -18302,7 +18308,7 @@
         <v>8</v>
       </c>
       <c r="Q77" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R77" t="n">
         <v>13</v>
@@ -18343,28 +18349,28 @@
         <v>1</v>
       </c>
       <c r="AT77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA77" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB77" t="n">
         <v>10</v>
@@ -18399,28 +18405,28 @@
         <v>2</v>
       </c>
       <c r="CB77" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CC77" t="n">
-        <v>0.75</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CD77" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CE77" t="n">
-        <v>0.35</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CF77" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CG77" t="n">
-        <v>0.5</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CH77" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI77" t="n">
-        <v>0.85</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CJ77" t="n">
         <v>0.4</v>
@@ -18455,13 +18461,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ77" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="DK77" t="n">
-        <v>458</v>
+        <v>480</v>
       </c>
       <c r="DL77" t="n">
-        <v>5.088888888888889</v>
+        <v>5.052631578947368</v>
       </c>
     </row>
     <row r="78">
@@ -18729,7 +18735,7 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K79" t="n">
         <v>20</v>
@@ -18738,7 +18744,7 @@
         <v>14</v>
       </c>
       <c r="M79" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
         <v>12</v>
@@ -18750,7 +18756,7 @@
         <v>22</v>
       </c>
       <c r="Q79" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R79" t="n">
         <v>18</v>
@@ -18791,28 +18797,28 @@
         <v>4</v>
       </c>
       <c r="AT79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AU79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AV79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AW79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AX79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AY79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BA79" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BB79" t="n">
         <v>28</v>
@@ -18847,28 +18853,28 @@
         <v>4</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="CC79" t="n">
-        <v>0.6052631578947368</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.3157894736842105</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="CE79" t="n">
-        <v>0.5</v>
+        <v>0.4871794871794872</v>
       </c>
       <c r="CF79" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CG79" t="n">
-        <v>0.5</v>
+        <v>0.5641025641025641</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6410256410256411</v>
       </c>
       <c r="CJ79" t="n">
         <v>0.2857142857142857</v>
@@ -18903,13 +18909,13 @@
         <v>1</v>
       </c>
       <c r="DJ79" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="DK79" t="n">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="DL79" t="n">
-        <v>5.085365853658536</v>
+        <v>5.06508875739645</v>
       </c>
     </row>
     <row r="80">
@@ -19174,7 +19180,7 @@
         <v>8</v>
       </c>
       <c r="K81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L81" t="n">
         <v>12</v>
@@ -19237,31 +19243,31 @@
         <v>5</v>
       </c>
       <c r="AT81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB81" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC81" t="n">
         <v>3</v>
@@ -19297,31 +19303,31 @@
         <v>6</v>
       </c>
       <c r="CB81" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CC81" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CE81" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CF81" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CG81" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CH81" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK81" t="n">
         <v>0.6666666666666666</v>
@@ -19412,7 +19418,7 @@
         <v>16</v>
       </c>
       <c r="K82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L82" t="n">
         <v>25</v>
@@ -19475,31 +19481,31 @@
         <v>5</v>
       </c>
       <c r="AT82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AU82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AV82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AW82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AX82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AY82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AZ82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BA82" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BB82" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC82" t="n">
         <v>3</v>
@@ -19535,31 +19541,31 @@
         <v>6</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CC82" t="n">
-        <v>0.55</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.3</v>
+        <v>0.2926829268292683</v>
       </c>
       <c r="CE82" t="n">
-        <v>0.625</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CF82" t="n">
-        <v>0.475</v>
+        <v>0.4634146341463415</v>
       </c>
       <c r="CG82" t="n">
-        <v>0.525</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.4</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.5</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.3125</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="CK82" t="n">
         <v>0.6666666666666666</v>
@@ -19648,7 +19654,7 @@
         <v>13</v>
       </c>
       <c r="K83" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L83" t="n">
         <v>12</v>
@@ -19672,7 +19678,7 @@
         <v>6</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T83" t="n">
         <v>9</v>
@@ -19703,31 +19709,31 @@
       <c r="AR83" t="inlineStr"/>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA83" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
@@ -19757,31 +19763,31 @@
         <v>0</v>
       </c>
       <c r="CB83" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CC83" t="n">
-        <v>0.25</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CD83" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CE83" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF83" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CG83" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.3</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CI83" t="n">
-        <v>0.75</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="CK83" t="inlineStr"/>
       <c r="CL83" t="inlineStr"/>
@@ -19809,13 +19815,13 @@
       <c r="DH83" t="inlineStr"/>
       <c r="DI83" t="inlineStr"/>
       <c r="DJ83" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="DK83" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="DL83" t="n">
-        <v>5.090909090909091</v>
+        <v>5.155555555555556</v>
       </c>
     </row>
     <row r="84">
@@ -20076,7 +20082,7 @@
         <v>24</v>
       </c>
       <c r="K85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L85" t="n">
         <v>20</v>
@@ -20100,7 +20106,7 @@
         <v>15</v>
       </c>
       <c r="S85" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="T85" t="n">
         <v>21</v>
@@ -20131,31 +20137,31 @@
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA85" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB85" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
@@ -20185,31 +20191,31 @@
         <v>0</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5</v>
       </c>
       <c r="CC85" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.475</v>
       </c>
       <c r="CD85" t="n">
-        <v>1</v>
+        <v>0.975</v>
       </c>
       <c r="CE85" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5</v>
       </c>
       <c r="CF85" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CG85" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.55</v>
       </c>
       <c r="CH85" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.375</v>
       </c>
       <c r="CI85" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.625</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.75</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="CK85" t="inlineStr"/>
       <c r="CL85" t="inlineStr"/>
@@ -20237,13 +20243,13 @@
       <c r="DH85" t="inlineStr"/>
       <c r="DI85" t="inlineStr"/>
       <c r="DJ85" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="DK85" t="n">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="DL85" t="n">
-        <v>4.850746268656716</v>
+        <v>4.881773399014778</v>
       </c>
     </row>
     <row r="86">
@@ -20287,7 +20293,7 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K86" t="n">
         <v>10</v>
@@ -20317,10 +20323,10 @@
         <v>11</v>
       </c>
       <c r="T86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V86" t="n">
         <v>1</v>
@@ -20350,37 +20356,37 @@
       <c r="AQ86" t="inlineStr"/>
       <c r="AR86" t="inlineStr"/>
       <c r="AS86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA86" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB86" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD86" t="n">
         <v>1</v>
@@ -20410,34 +20416,34 @@
       <c r="BY86" t="inlineStr"/>
       <c r="BZ86" t="inlineStr"/>
       <c r="CA86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB86" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CC86" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="CD86" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CE86" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CF86" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="CG86" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CH86" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CI86" t="n">
-        <v>0.5</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CJ86" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="CK86" t="n">
         <v>1</v>
@@ -20470,16 +20476,16 @@
       <c r="DG86" t="inlineStr"/>
       <c r="DH86" t="inlineStr"/>
       <c r="DI86" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DJ86" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="DK86" t="n">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="DL86" t="n">
-        <v>5.622222222222222</v>
+        <v>5.741935483870968</v>
       </c>
     </row>
     <row r="87">
@@ -20737,7 +20743,7 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K88" t="n">
         <v>16</v>
@@ -20767,10 +20773,10 @@
         <v>20</v>
       </c>
       <c r="T88" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="U88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V88" t="n">
         <v>1</v>
@@ -20800,37 +20806,37 @@
       <c r="AQ88" t="inlineStr"/>
       <c r="AR88" t="inlineStr"/>
       <c r="AS88" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA88" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB88" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD88" t="n">
         <v>1</v>
@@ -20860,34 +20866,34 @@
       <c r="BY88" t="inlineStr"/>
       <c r="BZ88" t="inlineStr"/>
       <c r="CA88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB88" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2</v>
       </c>
       <c r="CC88" t="n">
-        <v>0.282051282051282</v>
+        <v>0.275</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4</v>
       </c>
       <c r="CE88" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.525</v>
       </c>
       <c r="CF88" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CG88" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.375</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.45</v>
       </c>
       <c r="CI88" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9032258064516129</v>
       </c>
       <c r="CK88" t="n">
         <v>1</v>
@@ -20920,16 +20926,16 @@
       <c r="DG88" t="inlineStr"/>
       <c r="DH88" t="inlineStr"/>
       <c r="DI88" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DJ88" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="DK88" t="n">
-        <v>971</v>
+        <v>999</v>
       </c>
       <c r="DL88" t="n">
-        <v>5.81437125748503</v>
+        <v>5.876470588235295</v>
       </c>
     </row>
     <row r="89">
@@ -20973,7 +20979,7 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K89" t="n">
         <v>12</v>
@@ -20985,16 +20991,16 @@
         <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
         <v>9</v>
       </c>
       <c r="Q89" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R89" t="n">
         <v>10</v>
@@ -21005,9 +21011,15 @@
       <c r="T89" t="n">
         <v>2</v>
       </c>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="U89" t="n">
+        <v>2</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>1</v>
+      </c>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
@@ -21029,37 +21041,45 @@
       <c r="AP89" t="inlineStr"/>
       <c r="AQ89" t="inlineStr"/>
       <c r="AR89" t="inlineStr"/>
-      <c r="AS89" t="inlineStr"/>
+      <c r="AS89" t="n">
+        <v>3</v>
+      </c>
       <c r="AT89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA89" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB89" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC89" t="inlineStr"/>
-      <c r="BD89" t="inlineStr"/>
-      <c r="BE89" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE89" t="n">
+        <v>1</v>
+      </c>
       <c r="BF89" t="inlineStr"/>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
@@ -21082,38 +21102,44 @@
       <c r="BY89" t="inlineStr"/>
       <c r="BZ89" t="inlineStr"/>
       <c r="CA89" t="n">
+        <v>3</v>
+      </c>
+      <c r="CB89" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CC89" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="CD89" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CE89" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="CF89" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="CG89" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="CH89" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="CI89" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+      <c r="CJ89" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="CK89" t="n">
+        <v>2</v>
+      </c>
+      <c r="CL89" t="n">
         <v>0</v>
       </c>
-      <c r="CB89" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="CC89" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CD89" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CE89" t="n">
-        <v>0.09523809523809523</v>
-      </c>
-      <c r="CF89" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="CG89" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="CH89" t="n">
-        <v>0.4761904761904762</v>
-      </c>
-      <c r="CI89" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="CJ89" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="CK89" t="inlineStr"/>
-      <c r="CL89" t="inlineStr"/>
-      <c r="CM89" t="inlineStr"/>
+      <c r="CM89" t="n">
+        <v>1</v>
+      </c>
       <c r="CN89" t="inlineStr"/>
       <c r="CO89" t="inlineStr"/>
       <c r="CP89" t="inlineStr"/>
@@ -21135,15 +21161,17 @@
       <c r="DF89" t="inlineStr"/>
       <c r="DG89" t="inlineStr"/>
       <c r="DH89" t="inlineStr"/>
-      <c r="DI89" t="inlineStr"/>
+      <c r="DI89" t="n">
+        <v>1</v>
+      </c>
       <c r="DJ89" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="DK89" t="n">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="DL89" t="n">
-        <v>4.970149253731344</v>
+        <v>5.189189189189189</v>
       </c>
     </row>
     <row r="90">
@@ -21423,7 +21451,7 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K91" t="n">
         <v>24</v>
@@ -21435,16 +21463,16 @@
         <v>13</v>
       </c>
       <c r="N91" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O91" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P91" t="n">
         <v>12</v>
       </c>
       <c r="Q91" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R91" t="n">
         <v>20</v>
@@ -21456,13 +21484,13 @@
         <v>6</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
@@ -21486,43 +21514,43 @@
       <c r="AQ91" t="inlineStr"/>
       <c r="AR91" t="inlineStr"/>
       <c r="AS91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AT91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AU91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AV91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AW91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AX91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AY91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AZ91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BA91" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="BB91" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BC91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BF91" t="inlineStr"/>
       <c r="BG91" t="inlineStr"/>
@@ -21546,37 +21574,37 @@
       <c r="BY91" t="inlineStr"/>
       <c r="BZ91" t="inlineStr"/>
       <c r="CA91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.4358974358974359</v>
+        <v>0.425</v>
       </c>
       <c r="CC91" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.325</v>
       </c>
       <c r="CD91" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.325</v>
       </c>
       <c r="CE91" t="n">
-        <v>0.2564102564102564</v>
+        <v>0.275</v>
       </c>
       <c r="CF91" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3</v>
       </c>
       <c r="CG91" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.65</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.2</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.2</v>
+        <v>0.1935483870967742</v>
       </c>
       <c r="CK91" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="CL91" t="n">
         <v>0</v>
@@ -21606,16 +21634,16 @@
       <c r="DG91" t="inlineStr"/>
       <c r="DH91" t="inlineStr"/>
       <c r="DI91" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="DJ91" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="DK91" t="n">
-        <v>593</v>
+        <v>644</v>
       </c>
       <c r="DL91" t="n">
-        <v>4.821138211382114</v>
+        <v>4.953846153846154</v>
       </c>
     </row>
   </sheetData>

--- a/offense.xlsx
+++ b/offense.xlsx
@@ -989,31 +989,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>14</v>
       </c>
       <c r="P2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="S2" t="n">
         <v>6</v>
@@ -1051,31 +1051,31 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
         <v>1</v>
@@ -1107,31 +1107,31 @@
         <v>1</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="CC2" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CE2" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="CG2" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CF2" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="CH2" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
@@ -1163,13 +1163,13 @@
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="DK2" t="n">
-        <v>500</v>
+        <v>563</v>
       </c>
       <c r="DL2" t="n">
-        <v>5.05050505050505</v>
+        <v>5.072072072072072</v>
       </c>
     </row>
     <row r="3">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
         <v>17</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
         <v>24</v>
       </c>
       <c r="P4" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q4" t="n">
         <v>28</v>
       </c>
-      <c r="Q4" t="n">
-        <v>24</v>
-      </c>
       <c r="R4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1523,31 +1523,31 @@
         <v>6</v>
       </c>
       <c r="AT4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC4" t="n">
         <v>2</v>
@@ -1583,31 +1583,31 @@
         <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.40625</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
@@ -1643,13 +1643,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ4" t="n">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="DK4" t="n">
-        <v>977</v>
+        <v>1040</v>
       </c>
       <c r="DL4" t="n">
-        <v>5.397790055248619</v>
+        <v>5.38860103626943</v>
       </c>
     </row>
     <row r="5">
@@ -1697,16 +1697,16 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5" t="n">
         <v>14</v>
@@ -1718,10 +1718,10 @@
         <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1759,31 +1759,31 @@
         <v>1</v>
       </c>
       <c r="AT5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC5" t="n">
         <v>2</v>
@@ -1815,31 +1815,31 @@
         <v>2</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.7368421052631579</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="CK5" t="n">
         <v>0.5</v>
@@ -1871,13 +1871,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ5" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="DK5" t="n">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="DL5" t="n">
-        <v>4.892857142857143</v>
+        <v>4.916666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -2159,16 +2159,16 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
         <v>9</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -2180,10 +2180,10 @@
         <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S7" t="n">
         <v>7</v>
@@ -2223,31 +2223,31 @@
         <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC7" t="n">
         <v>3</v>
@@ -2281,31 +2281,31 @@
         <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.225</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.325</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.75</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.375</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.475</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.175</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="CK7" t="n">
         <v>0.3333333333333333</v>
@@ -2339,13 +2339,13 @@
         <v>0.25</v>
       </c>
       <c r="DJ7" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="DK7" t="n">
-        <v>798</v>
+        <v>819</v>
       </c>
       <c r="DL7" t="n">
-        <v>5.115384615384615</v>
+        <v>5.11875</v>
       </c>
     </row>
     <row r="8">
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
         <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -2665,31 +2665,31 @@
         <v>2</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC9" t="n">
         <v>2</v>
@@ -2721,31 +2721,31 @@
         <v>2</v>
       </c>
       <c r="CB9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="CG9" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CC9" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>0.2380952380952381</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>0.7619047619047619</v>
-      </c>
       <c r="CH9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.375</v>
       </c>
       <c r="CK9" t="n">
         <v>1</v>
@@ -2777,13 +2777,13 @@
         <v>1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="DK9" t="n">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="DL9" t="n">
-        <v>5.059523809523809</v>
+        <v>4.858695652173913</v>
       </c>
     </row>
     <row r="10">
@@ -2827,19 +2827,19 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M10" t="n">
         <v>24</v>
       </c>
       <c r="N10" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O10" t="n">
         <v>9</v>
@@ -2889,31 +2889,31 @@
         <v>2</v>
       </c>
       <c r="AT10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA10" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB10" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BC10" t="n">
         <v>2</v>
@@ -2945,31 +2945,31 @@
         <v>2</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.2045454545454546</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.8409090909090909</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.5517241379310345</v>
+        <v>0.5</v>
       </c>
       <c r="CK10" t="n">
         <v>1</v>
@@ -3001,13 +3001,13 @@
         <v>1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="DK10" t="n">
-        <v>1081</v>
+        <v>1103</v>
       </c>
       <c r="DL10" t="n">
-        <v>5.027906976744186</v>
+        <v>4.946188340807175</v>
       </c>
     </row>
     <row r="11">
@@ -3283,31 +3283,31 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" t="n">
         <v>12</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="n">
         <v>9</v>
       </c>
-      <c r="L12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M12" t="n">
-        <v>9</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>7</v>
       </c>
-      <c r="O12" t="n">
-        <v>6</v>
-      </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -3316,7 +3316,7 @@
         <v>13</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V12" t="n">
         <v>1</v>
@@ -3348,37 +3348,37 @@
       <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="inlineStr"/>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AT12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>1</v>
@@ -3410,37 +3410,37 @@
       <c r="BY12" t="inlineStr"/>
       <c r="BZ12" t="inlineStr"/>
       <c r="CA12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.5</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CD12" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CI12" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="CE12" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>0.3809523809523809</v>
-      </c>
       <c r="CJ12" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.333333333333333</v>
+        <v>1.6</v>
       </c>
       <c r="CL12" t="n">
         <v>1</v>
@@ -3472,16 +3472,16 @@
       <c r="DG12" t="inlineStr"/>
       <c r="DH12" t="inlineStr"/>
       <c r="DI12" t="n">
-        <v>1.166666666666667</v>
+        <v>1.375</v>
       </c>
       <c r="DJ12" t="n">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="DK12" t="n">
-        <v>546</v>
+        <v>636</v>
       </c>
       <c r="DL12" t="n">
-        <v>5.747368421052632</v>
+        <v>5.628318584070796</v>
       </c>
     </row>
     <row r="13">
@@ -3529,31 +3529,31 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="S13" t="n">
         <v>19</v>
@@ -3562,7 +3562,7 @@
         <v>17</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
@@ -3594,37 +3594,37 @@
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AT13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AU13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AV13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AW13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AX13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AY13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AZ13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BA13" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD13" t="n">
         <v>1</v>
@@ -3656,37 +3656,37 @@
       <c r="BY13" t="inlineStr"/>
       <c r="BZ13" t="inlineStr"/>
       <c r="CA13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.4</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="CL13" t="n">
         <v>1</v>
@@ -3718,16 +3718,16 @@
       <c r="DG13" t="inlineStr"/>
       <c r="DH13" t="inlineStr"/>
       <c r="DI13" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="DJ13" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="DK13" t="n">
-        <v>926</v>
+        <v>1016</v>
       </c>
       <c r="DL13" t="n">
-        <v>5.415204678362573</v>
+        <v>5.375661375661376</v>
       </c>
     </row>
     <row r="14">
@@ -3775,16 +3775,16 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L14" t="n">
         <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
         <v>13</v>
@@ -3799,16 +3799,16 @@
         <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
         <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V14" t="n">
         <v>1</v>
@@ -3836,37 +3836,37 @@
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="inlineStr"/>
       <c r="AS14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>1</v>
@@ -3894,37 +3894,37 @@
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr"/>
       <c r="CA14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.75</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="CL14" t="n">
         <v>1</v>
@@ -3952,16 +3952,16 @@
       <c r="DG14" t="inlineStr"/>
       <c r="DH14" t="inlineStr"/>
       <c r="DI14" t="n">
-        <v>0.6666666666666666</v>
+        <v>1.4</v>
       </c>
       <c r="DJ14" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="DK14" t="n">
-        <v>490</v>
+        <v>603</v>
       </c>
       <c r="DL14" t="n">
-        <v>5.268817204301075</v>
+        <v>5.532110091743119</v>
       </c>
     </row>
     <row r="15">
@@ -4237,16 +4237,16 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L16" t="n">
         <v>21</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N16" t="n">
         <v>18</v>
@@ -4261,16 +4261,16 @@
         <v>20</v>
       </c>
       <c r="R16" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="S16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T16" t="n">
         <v>12</v>
       </c>
       <c r="U16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V16" t="n">
         <v>1</v>
@@ -4298,37 +4298,37 @@
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="inlineStr"/>
       <c r="AS16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>43</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>43</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>43</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>33</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>40</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4</v>
       </c>
       <c r="BD16" t="n">
         <v>1</v>
@@ -4356,37 +4356,37 @@
       <c r="BY16" t="inlineStr"/>
       <c r="BZ16" t="inlineStr"/>
       <c r="CA16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.525</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.175</v>
+        <v>0.2325581395348837</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.45</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.375</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.525</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.5</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.425</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.675</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="CL16" t="n">
         <v>1</v>
@@ -4414,16 +4414,16 @@
       <c r="DG16" t="inlineStr"/>
       <c r="DH16" t="inlineStr"/>
       <c r="DI16" t="n">
-        <v>1.2</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="DJ16" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="DK16" t="n">
-        <v>878</v>
+        <v>991</v>
       </c>
       <c r="DL16" t="n">
-        <v>5.353658536585366</v>
+        <v>5.505555555555556</v>
       </c>
     </row>
     <row r="17">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K17" t="n">
         <v>9</v>
@@ -4476,25 +4476,25 @@
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q17" t="n">
         <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
         <v>8</v>
@@ -4529,28 +4529,28 @@
         <v>5</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -4585,28 +4585,28 @@
         <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.85</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.55</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6</v>
       </c>
       <c r="CJ17" t="n">
         <v>0.7272727272727273</v>
@@ -4641,13 +4641,13 @@
         <v>1.25</v>
       </c>
       <c r="DJ17" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="DK17" t="n">
-        <v>407</v>
+        <v>464</v>
       </c>
       <c r="DL17" t="n">
-        <v>5.652777777777778</v>
+        <v>5.523809523809524</v>
       </c>
     </row>
     <row r="18">
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
         <v>21</v>
@@ -4930,25 +4930,25 @@
         <v>23</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q19" t="n">
         <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T19" t="n">
         <v>15</v>
@@ -4985,28 +4985,28 @@
         <v>5</v>
       </c>
       <c r="AT19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB19" t="n">
         <v>33</v>
@@ -5043,28 +5043,28 @@
         <v>6</v>
       </c>
       <c r="CB19" t="n">
-        <v>0.575</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CC19" t="n">
-        <v>0.625</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.7</v>
+        <v>0.6904761904761905</v>
       </c>
       <c r="CE19" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CF19" t="n">
-        <v>0.25</v>
+        <v>0.4047619047619048</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.275</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.625</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.325</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CJ19" t="n">
         <v>0.4545454545454545</v>
@@ -5101,13 +5101,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ19" t="n">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="DK19" t="n">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="DL19" t="n">
-        <v>4.684210526315789</v>
+        <v>4.688524590163935</v>
       </c>
     </row>
     <row r="20">
@@ -5155,31 +5155,31 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
         <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O20" t="n">
         <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -5219,28 +5219,28 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AY20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB20" t="n">
         <v>10</v>
@@ -5277,28 +5277,28 @@
         <v>2</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="CC20" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CD20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CE20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CF20" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CG20" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CH20" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CI20" t="n">
-        <v>1.052631578947368</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="CJ20" t="n">
         <v>0.1</v>
@@ -5335,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="DJ20" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="DK20" t="n">
-        <v>370</v>
+        <v>415</v>
       </c>
       <c r="DL20" t="n">
-        <v>5.285714285714286</v>
+        <v>4.940476190476191</v>
       </c>
     </row>
     <row r="21">
@@ -5617,31 +5617,31 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K22" t="n">
         <v>21</v>
       </c>
       <c r="L22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S22" t="n">
         <v>36</v>
@@ -5681,28 +5681,28 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AU22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AV22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AW22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AX22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AY22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AZ22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BA22" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="BB22" t="n">
         <v>33</v>
@@ -5739,28 +5739,28 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.6</v>
       </c>
       <c r="CC22" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="CD22" t="n">
-        <v>0.3095238095238095</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CE22" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="CF22" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="CG22" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CH22" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6</v>
       </c>
       <c r="CI22" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8</v>
       </c>
       <c r="CJ22" t="n">
         <v>0.2727272727272727</v>
@@ -5797,13 +5797,13 @@
         <v>0.75</v>
       </c>
       <c r="DJ22" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="DK22" t="n">
-        <v>931</v>
+        <v>976</v>
       </c>
       <c r="DL22" t="n">
-        <v>5.381502890173411</v>
+        <v>5.219251336898396</v>
       </c>
     </row>
     <row r="23">
@@ -6072,13 +6072,13 @@
         <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L24" t="n">
+        <v>11</v>
+      </c>
+      <c r="M24" t="n">
         <v>9</v>
-      </c>
-      <c r="M24" t="n">
-        <v>7</v>
       </c>
       <c r="N24" t="n">
         <v>12</v>
@@ -6131,34 +6131,34 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AV24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AX24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="inlineStr"/>
@@ -6184,34 +6184,34 @@
       <c r="BY24" t="inlineStr"/>
       <c r="BZ24" t="inlineStr"/>
       <c r="CA24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB24" t="n">
-        <v>0.391304347826087</v>
+        <v>0.44</v>
       </c>
       <c r="CC24" t="n">
-        <v>0.3043478260869565</v>
+        <v>0.36</v>
       </c>
       <c r="CD24" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.48</v>
       </c>
       <c r="CE24" t="n">
-        <v>0.391304347826087</v>
+        <v>0.36</v>
       </c>
       <c r="CF24" t="n">
-        <v>0.2608695652173913</v>
+        <v>0.24</v>
       </c>
       <c r="CG24" t="n">
-        <v>0.391304347826087</v>
+        <v>0.36</v>
       </c>
       <c r="CH24" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.68</v>
       </c>
       <c r="CI24" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.48</v>
       </c>
       <c r="CJ24" t="n">
-        <v>0.391304347826087</v>
+        <v>0.36</v>
       </c>
       <c r="CK24" t="n">
         <v>0</v>
@@ -6243,13 +6243,13 @@
         <v>0</v>
       </c>
       <c r="DJ24" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="DK24" t="n">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="DL24" t="n">
-        <v>5.277777777777778</v>
+        <v>5.117021276595745</v>
       </c>
     </row>
     <row r="25">
@@ -6300,13 +6300,13 @@
         <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N25" t="n">
         <v>18</v>
@@ -6359,34 +6359,34 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="inlineStr"/>
@@ -6412,34 +6412,34 @@
       <c r="BY25" t="inlineStr"/>
       <c r="BZ25" t="inlineStr"/>
       <c r="CA25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB25" t="n">
-        <v>0.525</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CC25" t="n">
-        <v>0.275</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="CD25" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CE25" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF25" t="n">
-        <v>0.475</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CG25" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CH25" t="n">
-        <v>0.55</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CI25" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="CJ25" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="CK25" t="n">
         <v>0</v>
@@ -6471,13 +6471,13 @@
         <v>0</v>
       </c>
       <c r="DJ25" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="DK25" t="n">
-        <v>838</v>
+        <v>844</v>
       </c>
       <c r="DL25" t="n">
-        <v>5.109756097560975</v>
+        <v>5.023809523809524</v>
       </c>
     </row>
     <row r="26">
@@ -6760,10 +6760,10 @@
         <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
@@ -6772,13 +6772,13 @@
         <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P27" t="n">
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R27" t="n">
         <v>9</v>
@@ -6787,7 +6787,7 @@
         <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U27" t="n">
         <v>4</v>
@@ -6819,31 +6819,31 @@
         <v>4</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
         <v>2</v>
@@ -6875,31 +6875,31 @@
         <v>2</v>
       </c>
       <c r="CB27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="CC27" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="CD27" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="CE27" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="CF27" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.15</v>
       </c>
       <c r="CG27" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5</v>
       </c>
       <c r="CH27" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="CI27" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.35</v>
       </c>
       <c r="CJ27" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.35</v>
       </c>
       <c r="CK27" t="n">
         <v>2</v>
@@ -6931,13 +6931,13 @@
         <v>2</v>
       </c>
       <c r="DJ27" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="DK27" t="n">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="DL27" t="n">
-        <v>5.79245283018868</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -6984,10 +6984,10 @@
         <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M28" t="n">
         <v>15</v>
@@ -6996,13 +6996,13 @@
         <v>13</v>
       </c>
       <c r="O28" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P28" t="n">
         <v>7</v>
       </c>
       <c r="Q28" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R28" t="n">
         <v>26</v>
@@ -7011,7 +7011,7 @@
         <v>18</v>
       </c>
       <c r="T28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="U28" t="n">
         <v>7</v>
@@ -7047,31 +7047,31 @@
         <v>11</v>
       </c>
       <c r="AT28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB28" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -7107,31 +7107,31 @@
         <v>6</v>
       </c>
       <c r="CB28" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CC28" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CD28" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="CE28" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="CF28" t="n">
-        <v>0.1707317073170732</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="CG28" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CH28" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CI28" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CJ28" t="n">
-        <v>0.3225806451612903</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK28" t="n">
         <v>1.75</v>
@@ -7167,13 +7167,13 @@
         <v>1.833333333333333</v>
       </c>
       <c r="DJ28" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="DK28" t="n">
-        <v>935</v>
+        <v>985</v>
       </c>
       <c r="DL28" t="n">
-        <v>5.532544378698224</v>
+        <v>5.502793296089385</v>
       </c>
     </row>
     <row r="29">
@@ -7221,25 +7221,25 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
         <v>12</v>
       </c>
       <c r="N29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O29" t="n">
         <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q29" t="n">
         <v>5</v>
@@ -7248,7 +7248,7 @@
         <v>8</v>
       </c>
       <c r="S29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
         <v>5</v>
@@ -7283,31 +7283,31 @@
         <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
         <v>2</v>
@@ -7339,31 +7339,31 @@
         <v>2</v>
       </c>
       <c r="CB29" t="n">
-        <v>0.85</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CC29" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CD29" t="n">
-        <v>0.65</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CE29" t="n">
-        <v>0.8</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CF29" t="n">
-        <v>0.65</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CG29" t="n">
-        <v>0.25</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="CH29" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CI29" t="n">
-        <v>0.55</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CJ29" t="n">
-        <v>0.5</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CK29" t="n">
         <v>0</v>
@@ -7395,13 +7395,13 @@
         <v>0</v>
       </c>
       <c r="DJ29" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="DK29" t="n">
-        <v>428</v>
+        <v>465</v>
       </c>
       <c r="DL29" t="n">
-        <v>4.28</v>
+        <v>4.305555555555555</v>
       </c>
     </row>
     <row r="30">
@@ -7683,25 +7683,25 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
+        <v>24</v>
+      </c>
+      <c r="L31" t="n">
         <v>23</v>
-      </c>
-      <c r="L31" t="n">
-        <v>22</v>
       </c>
       <c r="M31" t="n">
         <v>25</v>
       </c>
       <c r="N31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O31" t="n">
         <v>24</v>
       </c>
       <c r="P31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q31" t="n">
         <v>11</v>
@@ -7710,7 +7710,7 @@
         <v>20</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T31" t="n">
         <v>18</v>
@@ -7747,31 +7747,31 @@
         <v>1</v>
       </c>
       <c r="AT31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA31" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC31" t="n">
         <v>3</v>
@@ -7805,31 +7805,31 @@
         <v>4</v>
       </c>
       <c r="CB31" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CC31" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CD31" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CE31" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CF31" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CG31" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="CH31" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CI31" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CJ31" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.5625</v>
       </c>
       <c r="CK31" t="n">
         <v>0</v>
@@ -7863,13 +7863,13 @@
         <v>0.25</v>
       </c>
       <c r="DJ31" t="n">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="DK31" t="n">
-        <v>927</v>
+        <v>964</v>
       </c>
       <c r="DL31" t="n">
-        <v>4.778350515463917</v>
+        <v>4.772277227722772</v>
       </c>
     </row>
     <row r="32">
@@ -7917,16 +7917,16 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32" t="n">
         <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N32" t="n">
         <v>6</v>
@@ -7935,16 +7935,16 @@
         <v>13</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q32" t="n">
         <v>8</v>
       </c>
       <c r="R32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -7981,31 +7981,31 @@
         <v>4</v>
       </c>
       <c r="AT32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA32" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC32" t="n">
         <v>3</v>
@@ -8039,28 +8039,28 @@
         <v>4</v>
       </c>
       <c r="CB32" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CC32" t="n">
-        <v>0.6875</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="CD32" t="n">
-        <v>0.375</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE32" t="n">
-        <v>0.8125</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="CF32" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="CG32" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CH32" t="n">
-        <v>0.8125</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="CI32" t="n">
-        <v>0.375</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="CJ32" t="n">
         <v>0</v>
@@ -8097,13 +8097,13 @@
         <v>1</v>
       </c>
       <c r="DJ32" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="DK32" t="n">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="DL32" t="n">
-        <v>4.888888888888889</v>
+        <v>4.890109890109891</v>
       </c>
     </row>
     <row r="33">
@@ -8385,16 +8385,16 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
         <v>19</v>
       </c>
       <c r="M34" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N34" t="n">
         <v>26</v>
@@ -8403,16 +8403,16 @@
         <v>21</v>
       </c>
       <c r="P34" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q34" t="n">
         <v>13</v>
       </c>
       <c r="R34" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="T34" t="n">
         <v>11</v>
@@ -8449,31 +8449,31 @@
         <v>5</v>
       </c>
       <c r="AT34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB34" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BC34" t="n">
         <v>4</v>
@@ -8507,31 +8507,31 @@
         <v>6</v>
       </c>
       <c r="CB34" t="n">
-        <v>0.475</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CC34" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="CD34" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CE34" t="n">
-        <v>0.525</v>
+        <v>0.5</v>
       </c>
       <c r="CF34" t="n">
-        <v>0.675</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="CG34" t="n">
-        <v>0.325</v>
+        <v>0.3095238095238095</v>
       </c>
       <c r="CH34" t="n">
-        <v>0.55</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CI34" t="n">
-        <v>0.35</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ34" t="n">
-        <v>0.3235294117647059</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="CK34" t="n">
         <v>1</v>
@@ -8565,13 +8565,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ34" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="DK34" t="n">
-        <v>846</v>
+        <v>895</v>
       </c>
       <c r="DL34" t="n">
-        <v>4.806818181818182</v>
+        <v>4.811827956989247</v>
       </c>
     </row>
     <row r="35">
@@ -8619,40 +8619,40 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L35" t="n">
         <v>16</v>
       </c>
       <c r="M35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
         <v>7</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="n">
         <v>4</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
@@ -8678,37 +8678,37 @@
       <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="inlineStr"/>
       <c r="AS35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AU35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AV35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AY35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB35" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BC35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD35" t="inlineStr"/>
       <c r="BE35" t="inlineStr"/>
@@ -8734,34 +8734,34 @@
       <c r="BY35" t="inlineStr"/>
       <c r="BZ35" t="inlineStr"/>
       <c r="CA35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CB35" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CC35" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CD35" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CE35" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="CF35" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CG35" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CH35" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CI35" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CJ35" t="n">
-        <v>0.4</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="CK35" t="n">
         <v>1</v>
@@ -8793,13 +8793,13 @@
         <v>1</v>
       </c>
       <c r="DJ35" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="DK35" t="n">
-        <v>414</v>
+        <v>454</v>
       </c>
       <c r="DL35" t="n">
-        <v>4.5</v>
+        <v>4.585858585858586</v>
       </c>
     </row>
     <row r="36">
@@ -9075,40 +9075,40 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L37" t="n">
         <v>30</v>
       </c>
       <c r="M37" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O37" t="n">
         <v>18</v>
       </c>
       <c r="P37" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="R37" t="n">
         <v>14</v>
       </c>
       <c r="S37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T37" t="n">
         <v>13</v>
       </c>
       <c r="U37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
@@ -9134,37 +9134,37 @@
       <c r="AQ37" t="inlineStr"/>
       <c r="AR37" t="inlineStr"/>
       <c r="AS37" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>44</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>44</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>35</v>
+      </c>
+      <c r="BC37" t="n">
         <v>4</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>41</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>41</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>41</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>3</v>
       </c>
       <c r="BD37" t="inlineStr"/>
       <c r="BE37" t="inlineStr"/>
@@ -9190,37 +9190,37 @@
       <c r="BY37" t="inlineStr"/>
       <c r="BZ37" t="inlineStr"/>
       <c r="CA37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB37" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="CC37" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CD37" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CE37" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="CF37" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.75</v>
       </c>
       <c r="CG37" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="CH37" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="CI37" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="CJ37" t="n">
-        <v>0.40625</v>
+        <v>0.3714285714285714</v>
       </c>
       <c r="CK37" t="n">
-        <v>1.333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="CL37" t="inlineStr"/>
       <c r="CM37" t="inlineStr"/>
@@ -9246,16 +9246,16 @@
       <c r="DG37" t="inlineStr"/>
       <c r="DH37" t="inlineStr"/>
       <c r="DI37" t="n">
-        <v>1.333333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="DJ37" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="DK37" t="n">
-        <v>931</v>
+        <v>971</v>
       </c>
       <c r="DL37" t="n">
-        <v>4.75</v>
+        <v>4.783251231527093</v>
       </c>
     </row>
     <row r="38">
@@ -9540,7 +9540,7 @@
         <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L39" t="n">
         <v>12</v>
@@ -9555,19 +9555,19 @@
         <v>19</v>
       </c>
       <c r="P39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R39" t="n">
         <v>12</v>
       </c>
       <c r="S39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="T39" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
@@ -9599,31 +9599,31 @@
         <v>1</v>
       </c>
       <c r="AT39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AV39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AW39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AX39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AZ39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB39" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC39" t="n">
         <v>2</v>
@@ -9655,31 +9655,31 @@
         <v>2</v>
       </c>
       <c r="CB39" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CC39" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CD39" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="CE39" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="CF39" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.5</v>
       </c>
       <c r="CG39" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="CH39" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="CI39" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CJ39" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="CK39" t="n">
         <v>0.5</v>
@@ -9711,13 +9711,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ39" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="DK39" t="n">
-        <v>593</v>
+        <v>634</v>
       </c>
       <c r="DL39" t="n">
-        <v>5.112068965517241</v>
+        <v>5.19672131147541</v>
       </c>
     </row>
     <row r="40">
@@ -9768,7 +9768,7 @@
         <v>16</v>
       </c>
       <c r="K40" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
         <v>24</v>
@@ -9783,19 +9783,19 @@
         <v>32</v>
       </c>
       <c r="P40" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R40" t="n">
         <v>17</v>
       </c>
       <c r="S40" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U40" t="n">
         <v>4</v>
@@ -9829,31 +9829,31 @@
         <v>5</v>
       </c>
       <c r="AT40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB40" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="BC40" t="n">
         <v>5</v>
@@ -9887,31 +9887,31 @@
         <v>6</v>
       </c>
       <c r="CB40" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CC40" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5</v>
       </c>
       <c r="CD40" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CE40" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CF40" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.5227272727272727</v>
       </c>
       <c r="CG40" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CH40" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="CI40" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CJ40" t="n">
-        <v>0.3142857142857143</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CK40" t="n">
         <v>0.8</v>
@@ -9945,13 +9945,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ40" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="DK40" t="n">
-        <v>840</v>
+        <v>881</v>
       </c>
       <c r="DL40" t="n">
-        <v>4.745762711864407</v>
+        <v>4.814207650273224</v>
       </c>
     </row>
     <row r="41">
@@ -10227,37 +10227,37 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>9</v>
+      </c>
+      <c r="K42" t="n">
+        <v>12</v>
+      </c>
+      <c r="L42" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" t="n">
+        <v>13</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" t="n">
+        <v>9</v>
+      </c>
+      <c r="P42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6</v>
+      </c>
+      <c r="R42" t="n">
         <v>7</v>
-      </c>
-      <c r="K42" t="n">
-        <v>11</v>
-      </c>
-      <c r="L42" t="n">
-        <v>5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>9</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>5</v>
-      </c>
-      <c r="P42" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>5</v>
-      </c>
-      <c r="R42" t="n">
-        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
       </c>
       <c r="T42" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="U42" t="n">
         <v>4</v>
@@ -10291,34 +10291,34 @@
         <v>4</v>
       </c>
       <c r="AT42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD42" t="n">
         <v>1</v>
@@ -10346,37 +10346,37 @@
       <c r="BY42" t="inlineStr"/>
       <c r="BZ42" t="inlineStr"/>
       <c r="CA42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB42" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CC42" t="n">
-        <v>0.5</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CD42" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CE42" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF42" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CG42" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CH42" t="n">
         <v>0.3333333333333333</v>
       </c>
       <c r="CI42" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CJ42" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CK42" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="CL42" t="n">
         <v>0</v>
@@ -10404,16 +10404,16 @@
       <c r="DG42" t="inlineStr"/>
       <c r="DH42" t="inlineStr"/>
       <c r="DI42" t="n">
-        <v>1.333333333333333</v>
+        <v>1</v>
       </c>
       <c r="DJ42" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="DK42" t="n">
-        <v>386</v>
+        <v>459</v>
       </c>
       <c r="DL42" t="n">
-        <v>5.594202898550725</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="43">
@@ -10461,37 +10461,37 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>21</v>
+      </c>
+      <c r="K43" t="n">
+        <v>23</v>
+      </c>
+      <c r="L43" t="n">
+        <v>24</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16</v>
+      </c>
+      <c r="O43" t="n">
         <v>19</v>
       </c>
-      <c r="K43" t="n">
-        <v>22</v>
-      </c>
-      <c r="L43" t="n">
-        <v>23</v>
-      </c>
-      <c r="M43" t="n">
-        <v>16</v>
-      </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>20</v>
+      </c>
+      <c r="R43" t="n">
         <v>15</v>
-      </c>
-      <c r="O43" t="n">
-        <v>15</v>
-      </c>
-      <c r="P43" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>19</v>
-      </c>
-      <c r="R43" t="n">
-        <v>14</v>
       </c>
       <c r="S43" t="n">
         <v>17</v>
       </c>
       <c r="T43" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U43" t="n">
         <v>6</v>
@@ -10525,34 +10525,34 @@
         <v>6</v>
       </c>
       <c r="AT43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AU43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AV43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AW43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AX43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AY43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AZ43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BA43" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="BB43" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="BC43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD43" t="n">
         <v>1</v>
@@ -10580,37 +10580,37 @@
       <c r="BY43" t="inlineStr"/>
       <c r="BZ43" t="inlineStr"/>
       <c r="CA43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB43" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CC43" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CD43" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CE43" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.4318181818181818</v>
       </c>
       <c r="CF43" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="CG43" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="CH43" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="CI43" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3863636363636364</v>
       </c>
       <c r="CJ43" t="n">
-        <v>0.46875</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="CK43" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="CL43" t="n">
         <v>0</v>
@@ -10638,16 +10638,16 @@
       <c r="DG43" t="inlineStr"/>
       <c r="DH43" t="inlineStr"/>
       <c r="DI43" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DJ43" t="n">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="DK43" t="n">
-        <v>838</v>
+        <v>911</v>
       </c>
       <c r="DL43" t="n">
-        <v>5.017964071856287</v>
+        <v>4.978142076502732</v>
       </c>
     </row>
     <row r="44">
@@ -10695,25 +10695,25 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>11</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10</v>
+      </c>
+      <c r="L44" t="n">
+        <v>2</v>
+      </c>
+      <c r="M44" t="n">
         <v>9</v>
-      </c>
-      <c r="K44" t="n">
-        <v>9</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>8</v>
       </c>
       <c r="N44" t="n">
         <v>4</v>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Q44" t="n">
         <v>5</v>
@@ -10725,7 +10725,7 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr"/>
@@ -10753,31 +10753,31 @@
       <c r="AR44" t="inlineStr"/>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA44" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB44" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BC44" t="inlineStr"/>
       <c r="BD44" t="inlineStr"/>
@@ -10807,31 +10807,31 @@
         <v>0</v>
       </c>
       <c r="CB44" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="CC44" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CE44" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF44" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="CG44" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CH44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CI44" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CJ44" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CK44" t="inlineStr"/>
       <c r="CL44" t="inlineStr"/>
@@ -10859,13 +10859,13 @@
       <c r="DH44" t="inlineStr"/>
       <c r="DI44" t="inlineStr"/>
       <c r="DJ44" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="DK44" t="n">
-        <v>243</v>
+        <v>312</v>
       </c>
       <c r="DL44" t="n">
-        <v>4.86</v>
+        <v>4.952380952380953</v>
       </c>
     </row>
     <row r="45">
@@ -11141,25 +11141,25 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N46" t="n">
         <v>26</v>
       </c>
       <c r="O46" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P46" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="Q46" t="n">
         <v>12</v>
@@ -11171,7 +11171,7 @@
         <v>15</v>
       </c>
       <c r="T46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="U46" t="n">
         <v>2</v>
@@ -11203,31 +11203,31 @@
         <v>2</v>
       </c>
       <c r="AT46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA46" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB46" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC46" t="n">
         <v>1</v>
@@ -11259,31 +11259,31 @@
         <v>1</v>
       </c>
       <c r="CB46" t="n">
-        <v>0.35</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CC46" t="n">
-        <v>0.275</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="CD46" t="n">
-        <v>0.65</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CE46" t="n">
-        <v>0.4</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CF46" t="n">
-        <v>0.45</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CG46" t="n">
-        <v>0.3</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="CH46" t="n">
-        <v>0.375</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CI46" t="n">
-        <v>0.375</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CJ46" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="CK46" t="n">
         <v>2</v>
@@ -11315,13 +11315,13 @@
         <v>2</v>
       </c>
       <c r="DJ46" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="DK46" t="n">
-        <v>765</v>
+        <v>834</v>
       </c>
       <c r="DL46" t="n">
-        <v>5.134228187919463</v>
+        <v>5.148148148148148</v>
       </c>
     </row>
     <row r="47">
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
         <v>6</v>
@@ -11381,13 +11381,13 @@
         <v>12</v>
       </c>
       <c r="N47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O47" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q47" t="n">
         <v>12</v>
@@ -11396,7 +11396,7 @@
         <v>8</v>
       </c>
       <c r="S47" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T47" t="n">
         <v>8</v>
@@ -11431,28 +11431,28 @@
         <v>1</v>
       </c>
       <c r="AT47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA47" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB47" t="n">
         <v>8</v>
@@ -11487,28 +11487,28 @@
         <v>1</v>
       </c>
       <c r="CB47" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CC47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="CD47" t="n">
         <v>0.5</v>
       </c>
       <c r="CE47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.65</v>
       </c>
       <c r="CF47" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="CG47" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="CH47" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CI47" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.8</v>
       </c>
       <c r="CJ47" t="n">
         <v>1</v>
@@ -11543,13 +11543,13 @@
         <v>1</v>
       </c>
       <c r="DJ47" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="DK47" t="n">
-        <v>453</v>
+        <v>504</v>
       </c>
       <c r="DL47" t="n">
-        <v>4.978021978021978</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="48">
@@ -11825,7 +11825,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
         <v>13</v>
@@ -11837,13 +11837,13 @@
         <v>36</v>
       </c>
       <c r="N49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P49" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q49" t="n">
         <v>25</v>
@@ -11852,7 +11852,7 @@
         <v>14</v>
       </c>
       <c r="S49" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T49" t="n">
         <v>32</v>
@@ -11887,28 +11887,28 @@
         <v>1</v>
       </c>
       <c r="AT49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA49" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB49" t="n">
         <v>31</v>
@@ -11943,28 +11943,28 @@
         <v>2</v>
       </c>
       <c r="CB49" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CC49" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="CD49" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CE49" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CF49" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CG49" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CH49" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CI49" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CJ49" t="n">
         <v>1.032258064516129</v>
@@ -11999,13 +11999,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ49" t="n">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="DK49" t="n">
-        <v>1135</v>
+        <v>1186</v>
       </c>
       <c r="DL49" t="n">
-        <v>4.978070175438597</v>
+        <v>5.0042194092827</v>
       </c>
     </row>
     <row r="50">
@@ -12281,28 +12281,28 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
+        <v>11</v>
+      </c>
+      <c r="L51" t="n">
         <v>10</v>
       </c>
-      <c r="L51" t="n">
-        <v>8</v>
-      </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N51" t="n">
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P51" t="n">
         <v>9</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -12339,31 +12339,31 @@
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AV51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AW51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB51" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC51" t="inlineStr"/>
       <c r="BD51" t="inlineStr"/>
@@ -12393,31 +12393,31 @@
         <v>0</v>
       </c>
       <c r="CB51" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="CC51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="CD51" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="CE51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="CF51" t="n">
-        <v>0.6</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="CG51" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="CH51" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="CI51" t="n">
-        <v>0.8</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="CJ51" t="n">
-        <v>0.2</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="CK51" t="inlineStr"/>
       <c r="CL51" t="inlineStr"/>
@@ -12445,13 +12445,13 @@
       <c r="DH51" t="inlineStr"/>
       <c r="DI51" t="inlineStr"/>
       <c r="DJ51" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="DK51" t="n">
-        <v>279</v>
+        <v>307</v>
       </c>
       <c r="DL51" t="n">
-        <v>4.65</v>
+        <v>4.449275362318841</v>
       </c>
     </row>
     <row r="52">
@@ -12499,28 +12499,28 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N52" t="n">
         <v>13</v>
       </c>
       <c r="O52" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P52" t="n">
         <v>15</v>
       </c>
       <c r="Q52" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R52" t="n">
         <v>11</v>
@@ -12561,31 +12561,31 @@
         <v>2</v>
       </c>
       <c r="AT52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA52" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC52" t="n">
         <v>2</v>
@@ -12617,31 +12617,31 @@
         <v>2</v>
       </c>
       <c r="CB52" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="CC52" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CD52" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="CE52" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CF52" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CG52" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CH52" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="CI52" t="n">
-        <v>0.8536585365853658</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="CJ52" t="n">
-        <v>0.2758620689655172</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="CK52" t="n">
         <v>1</v>
@@ -12673,13 +12673,13 @@
         <v>1</v>
       </c>
       <c r="DJ52" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="DK52" t="n">
-        <v>830</v>
+        <v>858</v>
       </c>
       <c r="DL52" t="n">
-        <v>4.715909090909091</v>
+        <v>4.637837837837838</v>
       </c>
     </row>
     <row r="53">
@@ -12723,7 +12723,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
         <v>12</v>
@@ -12732,31 +12732,31 @@
         <v>13</v>
       </c>
       <c r="M53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N53" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P53" t="n">
         <v>8</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V53" t="n">
         <v>3</v>
@@ -12784,37 +12784,37 @@
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr"/>
       <c r="AS53" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA53" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB53" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD53" t="n">
         <v>1</v>
@@ -12842,31 +12842,31 @@
       <c r="BY53" t="inlineStr"/>
       <c r="BZ53" t="inlineStr"/>
       <c r="CA53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CB53" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.65</v>
       </c>
       <c r="CC53" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="CD53" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.4</v>
       </c>
       <c r="CE53" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.55</v>
       </c>
       <c r="CF53" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4</v>
       </c>
       <c r="CG53" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.45</v>
       </c>
       <c r="CH53" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.2</v>
       </c>
       <c r="CI53" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="CJ53" t="n">
         <v>0</v>
@@ -12900,16 +12900,16 @@
       <c r="DG53" t="inlineStr"/>
       <c r="DH53" t="inlineStr"/>
       <c r="DI53" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DJ53" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="DK53" t="n">
-        <v>296</v>
+        <v>372</v>
       </c>
       <c r="DL53" t="n">
-        <v>4.553846153846154</v>
+        <v>4.769230769230769</v>
       </c>
     </row>
     <row r="54">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K55" t="n">
         <v>25</v>
@@ -13192,31 +13192,31 @@
         <v>19</v>
       </c>
       <c r="M55" t="n">
+        <v>21</v>
+      </c>
+      <c r="N55" t="n">
+        <v>9</v>
+      </c>
+      <c r="O55" t="n">
         <v>19</v>
-      </c>
-      <c r="N55" t="n">
-        <v>8</v>
-      </c>
-      <c r="O55" t="n">
-        <v>18</v>
       </c>
       <c r="P55" t="n">
         <v>16</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="S55" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="T55" t="n">
         <v>5</v>
       </c>
       <c r="U55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V55" t="n">
         <v>3</v>
@@ -13244,37 +13244,37 @@
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr"/>
       <c r="AS55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>42</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>42</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>37</v>
+      </c>
+      <c r="BC55" t="n">
         <v>8</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>40</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>40</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB55" t="n">
-        <v>36</v>
-      </c>
-      <c r="BC55" t="n">
-        <v>7</v>
       </c>
       <c r="BD55" t="n">
         <v>2</v>
@@ -13302,37 +13302,37 @@
       <c r="BY55" t="inlineStr"/>
       <c r="BZ55" t="inlineStr"/>
       <c r="CA55" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CB55" t="n">
-        <v>0.475</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CC55" t="n">
-        <v>0.475</v>
+        <v>0.5</v>
       </c>
       <c r="CD55" t="n">
-        <v>0.2</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="CE55" t="n">
-        <v>0.45</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CF55" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CG55" t="n">
-        <v>0.525</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="CH55" t="n">
-        <v>0.2</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CI55" t="n">
-        <v>0.425</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CJ55" t="n">
-        <v>0.1388888888888889</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="CK55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="CL55" t="n">
         <v>1.5</v>
@@ -13360,16 +13360,16 @@
       <c r="DG55" t="inlineStr"/>
       <c r="DH55" t="inlineStr"/>
       <c r="DI55" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9</v>
       </c>
       <c r="DJ55" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="DK55" t="n">
-        <v>679</v>
+        <v>755</v>
       </c>
       <c r="DL55" t="n">
-        <v>4.884892086330935</v>
+        <v>4.967105263157895</v>
       </c>
     </row>
     <row r="56">
@@ -13643,19 +13643,19 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K57" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
         <v>5</v>
@@ -13705,31 +13705,31 @@
         <v>4</v>
       </c>
       <c r="AT57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB57" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC57" t="n">
         <v>2</v>
@@ -13761,31 +13761,31 @@
         <v>2</v>
       </c>
       <c r="CB57" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8421052631578947</v>
       </c>
       <c r="CC57" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CD57" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CE57" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CF57" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CG57" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05263157894736842</v>
       </c>
       <c r="CH57" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="CI57" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="CJ57" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="CK57" t="n">
         <v>2</v>
@@ -13817,13 +13817,13 @@
         <v>2</v>
       </c>
       <c r="DJ57" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="DK57" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="DL57" t="n">
-        <v>4.65</v>
+        <v>4.523809523809524</v>
       </c>
     </row>
     <row r="58">
@@ -13867,19 +13867,19 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>20</v>
+      </c>
+      <c r="K58" t="n">
+        <v>23</v>
+      </c>
+      <c r="L58" t="n">
+        <v>32</v>
+      </c>
+      <c r="M58" t="n">
+        <v>14</v>
+      </c>
+      <c r="N58" t="n">
         <v>19</v>
-      </c>
-      <c r="K58" t="n">
-        <v>22</v>
-      </c>
-      <c r="L58" t="n">
-        <v>31</v>
-      </c>
-      <c r="M58" t="n">
-        <v>13</v>
-      </c>
-      <c r="N58" t="n">
-        <v>18</v>
       </c>
       <c r="O58" t="n">
         <v>9</v>
@@ -13931,31 +13931,31 @@
         <v>7</v>
       </c>
       <c r="AT58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA58" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB58" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC58" t="n">
         <v>6</v>
@@ -13989,31 +13989,31 @@
         <v>7</v>
       </c>
       <c r="CB58" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CC58" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CD58" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CE58" t="n">
-        <v>0.2195121951219512</v>
+        <v>0.2093023255813954</v>
       </c>
       <c r="CF58" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CG58" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CH58" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CI58" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CJ58" t="n">
-        <v>0.34375</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="CK58" t="n">
         <v>1.166666666666667</v>
@@ -14047,13 +14047,13 @@
         <v>1</v>
       </c>
       <c r="DJ58" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="DK58" t="n">
-        <v>849</v>
+        <v>855</v>
       </c>
       <c r="DL58" t="n">
-        <v>4.994117647058824</v>
+        <v>4.942196531791907</v>
       </c>
     </row>
     <row r="59">
@@ -14341,7 +14341,7 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
         <v>9</v>
@@ -14350,16 +14350,16 @@
         <v>21</v>
       </c>
       <c r="M60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Q60" t="n">
         <v>8</v>
@@ -14368,13 +14368,13 @@
         <v>18</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T60" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V60" t="inlineStr"/>
       <c r="W60" t="inlineStr"/>
@@ -14400,37 +14400,37 @@
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD60" t="inlineStr"/>
       <c r="BE60" t="inlineStr"/>
@@ -14456,37 +14456,37 @@
       <c r="BY60" t="inlineStr"/>
       <c r="BZ60" t="inlineStr"/>
       <c r="CA60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CB60" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.875</v>
       </c>
       <c r="CC60" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CD60" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CE60" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.875</v>
       </c>
       <c r="CF60" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.625</v>
       </c>
       <c r="CG60" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CH60" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
       <c r="CI60" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.375</v>
       </c>
       <c r="CJ60" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CK60" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="CL60" t="inlineStr"/>
       <c r="CM60" t="inlineStr"/>
@@ -14512,16 +14512,16 @@
       <c r="DG60" t="inlineStr"/>
       <c r="DH60" t="inlineStr"/>
       <c r="DI60" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="DJ60" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="DK60" t="n">
-        <v>613</v>
+        <v>704</v>
       </c>
       <c r="DL60" t="n">
-        <v>5.239316239316239</v>
+        <v>5.214814814814815</v>
       </c>
     </row>
     <row r="61">
@@ -14569,7 +14569,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K61" t="n">
         <v>22</v>
@@ -14578,16 +14578,16 @@
         <v>39</v>
       </c>
       <c r="M61" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O61" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P61" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q61" t="n">
         <v>17</v>
@@ -14596,13 +14596,13 @@
         <v>29</v>
       </c>
       <c r="S61" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T61" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -14632,37 +14632,37 @@
       <c r="AQ61" t="inlineStr"/>
       <c r="AR61" t="inlineStr"/>
       <c r="AS61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AT61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA61" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB61" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="BC61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD61" t="n">
         <v>1</v>
@@ -14692,37 +14692,37 @@
       <c r="BY61" t="inlineStr"/>
       <c r="BZ61" t="inlineStr"/>
       <c r="CA61" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CB61" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="CC61" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CD61" t="n">
-        <v>0.3414634146341464</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CE61" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="CF61" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CG61" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CH61" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CI61" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="CJ61" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="CK61" t="n">
-        <v>1.333333333333333</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="CL61" t="n">
         <v>0</v>
@@ -14752,16 +14752,16 @@
       <c r="DG61" t="inlineStr"/>
       <c r="DH61" t="inlineStr"/>
       <c r="DI61" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="DJ61" t="n">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="DK61" t="n">
-        <v>1101</v>
+        <v>1192</v>
       </c>
       <c r="DL61" t="n">
-        <v>5.073732718894009</v>
+        <v>5.072340425531915</v>
       </c>
     </row>
     <row r="62">
@@ -15046,7 +15046,7 @@
         <v>9</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -15058,10 +15058,10 @@
         <v>14</v>
       </c>
       <c r="O63" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q63" t="n">
         <v>16</v>
@@ -15101,31 +15101,31 @@
       <c r="AR63" t="inlineStr"/>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BB63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC63" t="inlineStr"/>
       <c r="BD63" t="inlineStr"/>
@@ -15155,31 +15155,31 @@
         <v>0</v>
       </c>
       <c r="CB63" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="CC63" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="CD63" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="CE63" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.45</v>
       </c>
       <c r="CF63" t="n">
         <v>0.5</v>
       </c>
       <c r="CG63" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8</v>
       </c>
       <c r="CH63" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="CI63" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5</v>
       </c>
       <c r="CJ63" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="CK63" t="inlineStr"/>
       <c r="CL63" t="inlineStr"/>
@@ -15207,13 +15207,13 @@
       <c r="DH63" t="inlineStr"/>
       <c r="DI63" t="inlineStr"/>
       <c r="DJ63" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="DK63" t="n">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="DL63" t="n">
-        <v>5.527472527472527</v>
+        <v>5.48936170212766</v>
       </c>
     </row>
     <row r="64">
@@ -15264,7 +15264,7 @@
         <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L64" t="n">
         <v>15</v>
@@ -15276,10 +15276,10 @@
         <v>34</v>
       </c>
       <c r="O64" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P64" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q64" t="n">
         <v>26</v>
@@ -15325,31 +15325,31 @@
         <v>4</v>
       </c>
       <c r="AT64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA64" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB64" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC64" t="n">
         <v>5</v>
@@ -15383,31 +15383,31 @@
         <v>6</v>
       </c>
       <c r="CB64" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CC64" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CD64" t="n">
-        <v>0.8292682926829268</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="CE64" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CF64" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CG64" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CH64" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CI64" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CJ64" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="CK64" t="n">
         <v>0.8</v>
@@ -15441,13 +15441,13 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="DJ64" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="DK64" t="n">
-        <v>1078</v>
+        <v>1091</v>
       </c>
       <c r="DL64" t="n">
-        <v>5.013953488372093</v>
+        <v>5.004587155963303</v>
       </c>
     </row>
     <row r="65">
@@ -15498,19 +15498,19 @@
         <v>12</v>
       </c>
       <c r="K65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L65" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M65" t="n">
         <v>9</v>
       </c>
       <c r="N65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O65" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P65" t="n">
         <v>11</v>
@@ -15525,10 +15525,10 @@
         <v>14</v>
       </c>
       <c r="T65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V65" t="n">
         <v>1</v>
@@ -15556,37 +15556,37 @@
       <c r="AQ65" t="inlineStr"/>
       <c r="AR65" t="inlineStr"/>
       <c r="AS65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA65" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB65" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD65" t="n">
         <v>1</v>
@@ -15614,37 +15614,37 @@
       <c r="BY65" t="inlineStr"/>
       <c r="BZ65" t="inlineStr"/>
       <c r="CA65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="CB65" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="CC65" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CD65" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="CE65" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CF65" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="CG65" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CH65" t="n">
-        <v>0.1904761904761905</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="CI65" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="CJ65" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="CK65" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="CL65" t="n">
         <v>1</v>
@@ -15672,16 +15672,16 @@
       <c r="DG65" t="inlineStr"/>
       <c r="DH65" t="inlineStr"/>
       <c r="DI65" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="DJ65" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="DK65" t="n">
-        <v>412</v>
+        <v>456</v>
       </c>
       <c r="DL65" t="n">
-        <v>4.790697674418604</v>
+        <v>4.701030927835052</v>
       </c>
     </row>
     <row r="66">
@@ -15960,19 +15960,19 @@
         <v>22</v>
       </c>
       <c r="K67" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L67" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="M67" t="n">
         <v>15</v>
       </c>
       <c r="N67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P67" t="n">
         <v>18</v>
@@ -15987,10 +15987,10 @@
         <v>20</v>
       </c>
       <c r="T67" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="U67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V67" t="n">
         <v>1</v>
@@ -16018,37 +16018,37 @@
       <c r="AQ67" t="inlineStr"/>
       <c r="AR67" t="inlineStr"/>
       <c r="AS67" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA67" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB67" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD67" t="n">
         <v>1</v>
@@ -16076,37 +16076,37 @@
       <c r="BY67" t="inlineStr"/>
       <c r="BZ67" t="inlineStr"/>
       <c r="CA67" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB67" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7906976744186046</v>
       </c>
       <c r="CC67" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CD67" t="n">
-        <v>0.1463414634146341</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="CE67" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CF67" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="CG67" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CH67" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CI67" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="CK67" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="CL67" t="n">
         <v>1</v>
@@ -16134,16 +16134,16 @@
       <c r="DG67" t="inlineStr"/>
       <c r="DH67" t="inlineStr"/>
       <c r="DI67" t="n">
-        <v>1.333333333333333</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="DJ67" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="DK67" t="n">
-        <v>853</v>
+        <v>897</v>
       </c>
       <c r="DL67" t="n">
-        <v>5.201219512195122</v>
+        <v>5.125714285714285</v>
       </c>
     </row>
     <row r="68">
@@ -16191,10 +16191,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L68" t="n">
         <v>12</v>
@@ -16203,13 +16203,13 @@
         <v>10</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="P68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q68" t="n">
         <v>21</v>
@@ -16253,31 +16253,31 @@
         <v>3</v>
       </c>
       <c r="AT68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AY68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AZ68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA68" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC68" t="n">
         <v>3</v>
@@ -16309,31 +16309,31 @@
         <v>3</v>
       </c>
       <c r="CB68" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CC68" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="CD68" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CE68" t="n">
-        <v>1</v>
+        <v>1.130434782608696</v>
       </c>
       <c r="CF68" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="CG68" t="n">
-        <v>1</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="CH68" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="CI68" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="CJ68" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK68" t="n">
         <v>1</v>
@@ -16365,13 +16365,13 @@
         <v>1</v>
       </c>
       <c r="DJ68" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="DK68" t="n">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="DL68" t="n">
-        <v>5.103448275862069</v>
+        <v>5.040650406504065</v>
       </c>
     </row>
     <row r="69">
@@ -16647,10 +16647,10 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L70" t="n">
         <v>25</v>
@@ -16659,13 +16659,13 @@
         <v>13</v>
       </c>
       <c r="N70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O70" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P70" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q70" t="n">
         <v>26</v>
@@ -16709,31 +16709,31 @@
         <v>6</v>
       </c>
       <c r="AT70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AU70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AV70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AW70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AZ70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BA70" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB70" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC70" t="n">
         <v>4</v>
@@ -16765,31 +16765,31 @@
         <v>4</v>
       </c>
       <c r="CB70" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.625</v>
       </c>
       <c r="CC70" t="n">
-        <v>0.3421052631578947</v>
+        <v>0.325</v>
       </c>
       <c r="CD70" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4</v>
       </c>
       <c r="CE70" t="n">
-        <v>0.8157894736842105</v>
+        <v>0.9</v>
       </c>
       <c r="CF70" t="n">
-        <v>0.3947368421052632</v>
+        <v>0.4</v>
       </c>
       <c r="CG70" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.65</v>
       </c>
       <c r="CH70" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.525</v>
       </c>
       <c r="CI70" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8</v>
       </c>
       <c r="CJ70" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="CK70" t="n">
         <v>1.5</v>
@@ -16821,13 +16821,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ70" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="DK70" t="n">
-        <v>1013</v>
+        <v>1041</v>
       </c>
       <c r="DL70" t="n">
-        <v>5.194871794871795</v>
+        <v>5.153465346534653</v>
       </c>
     </row>
     <row r="71">
@@ -16871,31 +16871,31 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L71" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M71" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S71" t="n">
         <v>18</v>
@@ -16939,31 +16939,31 @@
         <v>2</v>
       </c>
       <c r="AT71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AV71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AY71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA71" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB71" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC71" t="n">
         <v>2</v>
@@ -17001,31 +17001,31 @@
         <v>5</v>
       </c>
       <c r="CB71" t="n">
-        <v>0.75</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="CC71" t="n">
-        <v>0.95</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="CD71" t="n">
-        <v>0.15</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="CE71" t="n">
-        <v>0.6</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="CF71" t="n">
-        <v>0.9</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="CG71" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="CH71" t="n">
-        <v>0.25</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="CI71" t="n">
-        <v>0.9</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="CJ71" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="CK71" t="n">
         <v>0</v>
@@ -17063,13 +17063,13 @@
         <v>0.4</v>
       </c>
       <c r="DJ71" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="DK71" t="n">
-        <v>565</v>
+        <v>591</v>
       </c>
       <c r="DL71" t="n">
-        <v>4.829059829059829</v>
+        <v>4.766129032258065</v>
       </c>
     </row>
     <row r="72">
@@ -17349,31 +17349,31 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K73" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L73" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M73" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O73" t="n">
         <v>16</v>
       </c>
       <c r="P73" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q73" t="n">
         <v>30</v>
       </c>
-      <c r="Q73" t="n">
-        <v>29</v>
-      </c>
       <c r="R73" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -17417,31 +17417,31 @@
         <v>12</v>
       </c>
       <c r="AT73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB73" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BC73" t="n">
         <v>7</v>
@@ -17479,31 +17479,31 @@
         <v>14</v>
       </c>
       <c r="CB73" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CC73" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="CD73" t="n">
-        <v>0.1951219512195122</v>
+        <v>0.2093023255813954</v>
       </c>
       <c r="CE73" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CF73" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="CG73" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.6976744186046512</v>
       </c>
       <c r="CH73" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CI73" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4651162790697674</v>
       </c>
       <c r="CJ73" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.625</v>
       </c>
       <c r="CK73" t="n">
         <v>1.142857142857143</v>
@@ -17541,13 +17541,13 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="DJ73" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="DK73" t="n">
-        <v>1058</v>
+        <v>1084</v>
       </c>
       <c r="DL73" t="n">
-        <v>5.135922330097087</v>
+        <v>5.089201877934272</v>
       </c>
     </row>
     <row r="74">
@@ -17829,13 +17829,13 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>14</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
         <v>13</v>
-      </c>
-      <c r="K75" t="n">
-        <v>6</v>
-      </c>
-      <c r="L75" t="n">
-        <v>9</v>
       </c>
       <c r="M75" t="n">
         <v>3</v>
@@ -17844,16 +17844,16 @@
         <v>9</v>
       </c>
       <c r="O75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P75" t="n">
         <v>23</v>
       </c>
       <c r="Q75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S75" t="n">
         <v>17</v>
@@ -17891,31 +17891,31 @@
         <v>5</v>
       </c>
       <c r="AT75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC75" t="n">
         <v>3</v>
@@ -17947,31 +17947,31 @@
         <v>3</v>
       </c>
       <c r="CB75" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CC75" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="CD75" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CE75" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CF75" t="n">
-        <v>1.210526315789474</v>
+        <v>1.095238095238095</v>
       </c>
       <c r="CG75" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CH75" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CI75" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="CJ75" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CK75" t="n">
         <v>1.666666666666667</v>
@@ -18003,13 +18003,13 @@
         <v>1.666666666666667</v>
       </c>
       <c r="DJ75" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="DK75" t="n">
-        <v>555</v>
+        <v>582</v>
       </c>
       <c r="DL75" t="n">
-        <v>5.663265306122449</v>
+        <v>5.490566037735849</v>
       </c>
     </row>
     <row r="76">
@@ -18057,13 +18057,13 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>24</v>
+      </c>
+      <c r="K76" t="n">
+        <v>17</v>
+      </c>
+      <c r="L76" t="n">
         <v>23</v>
-      </c>
-      <c r="K76" t="n">
-        <v>16</v>
-      </c>
-      <c r="L76" t="n">
-        <v>19</v>
       </c>
       <c r="M76" t="n">
         <v>8</v>
@@ -18072,16 +18072,16 @@
         <v>23</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P76" t="n">
         <v>25</v>
       </c>
       <c r="Q76" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R76" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S76" t="n">
         <v>30</v>
@@ -18121,31 +18121,31 @@
         <v>9</v>
       </c>
       <c r="AT76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AU76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AV76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AW76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AX76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AY76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="AZ76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BA76" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="BB76" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC76" t="n">
         <v>6</v>
@@ -18179,31 +18179,31 @@
         <v>7</v>
       </c>
       <c r="CB76" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CC76" t="n">
-        <v>0.2051282051282051</v>
+        <v>0.1951219512195122</v>
       </c>
       <c r="CD76" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="CE76" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="CF76" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="CG76" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5365853658536586</v>
       </c>
       <c r="CH76" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="CI76" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7317073170731707</v>
       </c>
       <c r="CJ76" t="n">
-        <v>0.3125</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="CK76" t="n">
         <v>1.333333333333333</v>
@@ -18237,13 +18237,13 @@
         <v>1.285714285714286</v>
       </c>
       <c r="DJ76" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="DK76" t="n">
-        <v>974</v>
+        <v>1001</v>
       </c>
       <c r="DL76" t="n">
-        <v>5.411111111111111</v>
+        <v>5.324468085106383</v>
       </c>
     </row>
     <row r="77">
@@ -18511,16 +18511,16 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K78" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N78" t="n">
         <v>6</v>
@@ -18532,16 +18532,16 @@
         <v>14</v>
       </c>
       <c r="Q78" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S78" t="n">
         <v>8</v>
       </c>
       <c r="T78" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="U78" t="n">
         <v>3</v>
@@ -18573,31 +18573,31 @@
         <v>3</v>
       </c>
       <c r="AT78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB78" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC78" t="n">
         <v>2</v>
@@ -18629,31 +18629,31 @@
         <v>2</v>
       </c>
       <c r="CB78" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CC78" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CD78" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CE78" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="CF78" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="CF78" t="n">
-        <v>0.7777777777777778</v>
-      </c>
       <c r="CG78" t="n">
-        <v>0.5</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CH78" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CI78" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CJ78" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="CK78" t="n">
         <v>1.5</v>
@@ -18685,13 +18685,13 @@
         <v>1.5</v>
       </c>
       <c r="DJ78" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="DK78" t="n">
-        <v>376</v>
+        <v>446</v>
       </c>
       <c r="DL78" t="n">
-        <v>5.081081081081081</v>
+        <v>5.309523809523809</v>
       </c>
     </row>
     <row r="79">
@@ -18735,16 +18735,16 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L79" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N79" t="n">
         <v>12</v>
@@ -18756,16 +18756,16 @@
         <v>22</v>
       </c>
       <c r="Q79" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R79" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
       </c>
       <c r="T79" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="U79" t="n">
         <v>4</v>
@@ -18797,31 +18797,31 @@
         <v>4</v>
       </c>
       <c r="AT79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AU79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AV79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AW79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AX79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AY79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AZ79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BA79" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="BB79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="BC79" t="n">
         <v>4</v>
@@ -18853,31 +18853,31 @@
         <v>4</v>
       </c>
       <c r="CB79" t="n">
-        <v>0.358974358974359</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="CC79" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CD79" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CE79" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CF79" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CG79" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CH79" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="CI79" t="n">
-        <v>0.6410256410256411</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="CJ79" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="CK79" t="n">
         <v>1</v>
@@ -18909,13 +18909,13 @@
         <v>1</v>
       </c>
       <c r="DJ79" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="DK79" t="n">
-        <v>856</v>
+        <v>926</v>
       </c>
       <c r="DL79" t="n">
-        <v>5.06508875739645</v>
+        <v>5.173184357541899</v>
       </c>
     </row>
     <row r="80">
@@ -19177,10 +19177,10 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K81" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L81" t="n">
         <v>12</v>
@@ -19195,7 +19195,7 @@
         <v>14</v>
       </c>
       <c r="P81" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q81" t="n">
         <v>10</v>
@@ -19204,10 +19204,10 @@
         <v>7</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U81" t="n">
         <v>2</v>
@@ -19243,31 +19243,31 @@
         <v>5</v>
       </c>
       <c r="AT81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AY81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB81" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC81" t="n">
         <v>3</v>
@@ -19303,31 +19303,31 @@
         <v>6</v>
       </c>
       <c r="CB81" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
       <c r="CC81" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.25</v>
       </c>
       <c r="CD81" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.375</v>
       </c>
       <c r="CE81" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CF81" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CG81" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CH81" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="CI81" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="CJ81" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.5</v>
       </c>
       <c r="CK81" t="n">
         <v>0.6666666666666666</v>
@@ -19363,13 +19363,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ81" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="DK81" t="n">
-        <v>448</v>
+        <v>522</v>
       </c>
       <c r="DL81" t="n">
-        <v>5.149425287356322</v>
+        <v>5.326530612244898</v>
       </c>
     </row>
     <row r="82">
@@ -19415,10 +19415,10 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K82" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L82" t="n">
         <v>25</v>
@@ -19433,7 +19433,7 @@
         <v>25</v>
       </c>
       <c r="P82" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="Q82" t="n">
         <v>21</v>
@@ -19442,10 +19442,10 @@
         <v>16</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T82" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U82" t="n">
         <v>2</v>
@@ -19481,31 +19481,31 @@
         <v>5</v>
       </c>
       <c r="AT82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AU82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AV82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AW82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AX82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AY82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AZ82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BA82" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="BB82" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="BC82" t="n">
         <v>3</v>
@@ -19541,31 +19541,31 @@
         <v>6</v>
       </c>
       <c r="CB82" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CC82" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CD82" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2790697674418605</v>
       </c>
       <c r="CE82" t="n">
-        <v>0.6097560975609756</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CF82" t="n">
-        <v>0.4634146341463415</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CG82" t="n">
-        <v>0.5121951219512195</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CH82" t="n">
-        <v>0.3902439024390244</v>
+        <v>0.3720930232558139</v>
       </c>
       <c r="CI82" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CJ82" t="n">
-        <v>0.303030303030303</v>
+        <v>0.4</v>
       </c>
       <c r="CK82" t="n">
         <v>0.6666666666666666</v>
@@ -19601,13 +19601,13 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="DJ82" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="DK82" t="n">
-        <v>841</v>
+        <v>915</v>
       </c>
       <c r="DL82" t="n">
-        <v>4.805714285714286</v>
+        <v>4.919354838709677</v>
       </c>
     </row>
     <row r="83">
@@ -19651,28 +19651,28 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>14</v>
+      </c>
+      <c r="K83" t="n">
+        <v>10</v>
+      </c>
+      <c r="L83" t="n">
         <v>13</v>
-      </c>
-      <c r="K83" t="n">
-        <v>8</v>
-      </c>
-      <c r="L83" t="n">
-        <v>12</v>
       </c>
       <c r="M83" t="n">
         <v>5</v>
       </c>
       <c r="N83" t="n">
+        <v>16</v>
+      </c>
+      <c r="O83" t="n">
         <v>13</v>
-      </c>
-      <c r="O83" t="n">
-        <v>9</v>
       </c>
       <c r="P83" t="n">
         <v>6</v>
       </c>
       <c r="Q83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R83" t="n">
         <v>6</v>
@@ -19709,31 +19709,31 @@
       <c r="AR83" t="inlineStr"/>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AU83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AV83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AW83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AX83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AZ83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BA83" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC83" t="inlineStr"/>
       <c r="BD83" t="inlineStr"/>
@@ -19763,31 +19763,31 @@
         <v>0</v>
       </c>
       <c r="CB83" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CC83" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="CD83" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="CE83" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="CF83" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="CG83" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="CH83" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
       <c r="CI83" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="CJ83" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="CK83" t="inlineStr"/>
       <c r="CL83" t="inlineStr"/>
@@ -19815,13 +19815,13 @@
       <c r="DH83" t="inlineStr"/>
       <c r="DI83" t="inlineStr"/>
       <c r="DJ83" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="DK83" t="n">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="DL83" t="n">
-        <v>5.155555555555556</v>
+        <v>5.01010101010101</v>
       </c>
     </row>
     <row r="84">
@@ -20079,28 +20079,28 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K85" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M85" t="n">
         <v>19</v>
       </c>
       <c r="N85" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O85" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P85" t="n">
         <v>22</v>
       </c>
       <c r="Q85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R85" t="n">
         <v>15</v>
@@ -20137,31 +20137,31 @@
       <c r="AR85" t="inlineStr"/>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA85" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB85" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="BC85" t="inlineStr"/>
       <c r="BD85" t="inlineStr"/>
@@ -20191,31 +20191,31 @@
         <v>0</v>
       </c>
       <c r="CB85" t="n">
-        <v>0.5</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="CC85" t="n">
-        <v>0.475</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="CD85" t="n">
-        <v>0.975</v>
+        <v>0.9767441860465116</v>
       </c>
       <c r="CE85" t="n">
-        <v>0.5</v>
+        <v>0.5581395348837209</v>
       </c>
       <c r="CF85" t="n">
-        <v>0.55</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="CG85" t="n">
-        <v>0.55</v>
+        <v>0.5348837209302325</v>
       </c>
       <c r="CH85" t="n">
-        <v>0.375</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="CI85" t="n">
-        <v>0.625</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="CJ85" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="CK85" t="inlineStr"/>
       <c r="CL85" t="inlineStr"/>
@@ -20243,13 +20243,13 @@
       <c r="DH85" t="inlineStr"/>
       <c r="DI85" t="inlineStr"/>
       <c r="DJ85" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="DK85" t="n">
-        <v>991</v>
+        <v>1023</v>
       </c>
       <c r="DL85" t="n">
-        <v>4.881773399014778</v>
+        <v>4.825471698113208</v>
       </c>
     </row>
     <row r="86">
@@ -20529,10 +20529,10 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -20544,22 +20544,22 @@
         <v>3</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P87" t="n">
         <v>13</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R87" t="n">
         <v>13</v>
       </c>
       <c r="S87" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U87" t="inlineStr"/>
       <c r="V87" t="inlineStr"/>
@@ -20587,31 +20587,31 @@
       <c r="AR87" t="inlineStr"/>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB87" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BC87" t="inlineStr"/>
       <c r="BD87" t="inlineStr"/>
@@ -20641,31 +20641,31 @@
         <v>0</v>
       </c>
       <c r="CB87" t="n">
-        <v>0.1176470588235294</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="CC87" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CD87" t="n">
-        <v>0.1764705882352941</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="CE87" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="CF87" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="CG87" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="CH87" t="n">
-        <v>0.7647058823529411</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="CI87" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="CJ87" t="n">
-        <v>0.9411764705882353</v>
+        <v>1</v>
       </c>
       <c r="CK87" t="inlineStr"/>
       <c r="CL87" t="inlineStr"/>
@@ -20693,13 +20693,13 @@
       <c r="DH87" t="inlineStr"/>
       <c r="DI87" t="inlineStr"/>
       <c r="DJ87" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="DK87" t="n">
-        <v>465</v>
+        <v>514</v>
       </c>
       <c r="DL87" t="n">
-        <v>6.038961038961039</v>
+        <v>6.119047619047619</v>
       </c>
     </row>
     <row r="88">
@@ -20743,10 +20743,10 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L88" t="n">
         <v>8</v>
@@ -20758,22 +20758,22 @@
         <v>16</v>
       </c>
       <c r="O88" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P88" t="n">
         <v>26</v>
       </c>
       <c r="Q88" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R88" t="n">
         <v>18</v>
       </c>
       <c r="S88" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T88" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U88" t="n">
         <v>2</v>
@@ -20809,31 +20809,31 @@
         <v>7</v>
       </c>
       <c r="AT88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AU88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AV88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AW88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AY88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AZ88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA88" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB88" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="BC88" t="n">
         <v>2</v>
@@ -20869,31 +20869,31 @@
         <v>4</v>
       </c>
       <c r="CB88" t="n">
-        <v>0.2</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="CC88" t="n">
-        <v>0.275</v>
+        <v>0.2619047619047619</v>
       </c>
       <c r="CD88" t="n">
-        <v>0.4</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CE88" t="n">
-        <v>0.525</v>
+        <v>0.5476190476190477</v>
       </c>
       <c r="CF88" t="n">
-        <v>0.65</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="CG88" t="n">
-        <v>0.375</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CH88" t="n">
-        <v>0.45</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="CI88" t="n">
         <v>0.5</v>
       </c>
       <c r="CJ88" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.9393939393939394</v>
       </c>
       <c r="CK88" t="n">
         <v>1</v>
@@ -20929,13 +20929,13 @@
         <v>1.75</v>
       </c>
       <c r="DJ88" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="DK88" t="n">
-        <v>999</v>
+        <v>1048</v>
       </c>
       <c r="DL88" t="n">
-        <v>5.876470588235295</v>
+        <v>5.92090395480226</v>
       </c>
     </row>
     <row r="89">
@@ -21215,37 +21215,37 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K90" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L90" t="n">
         <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R90" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -21281,31 +21281,31 @@
         <v>1</v>
       </c>
       <c r="AT90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AU90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AV90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AY90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AZ90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BB90" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BC90" t="n">
         <v>3</v>
@@ -21341,31 +21341,31 @@
         <v>5</v>
       </c>
       <c r="CB90" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CC90" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CD90" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="CE90" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3809523809523809</v>
       </c>
       <c r="CF90" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="CG90" t="n">
-        <v>0.5</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="CH90" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="CI90" t="n">
         <v>0</v>
       </c>
       <c r="CJ90" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="CK90" t="n">
         <v>0</v>
@@ -21401,13 +21401,13 @@
         <v>0.2</v>
       </c>
       <c r="DJ90" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="DK90" t="n">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="DL90" t="n">
-        <v>4.642857142857143</v>
+        <v>5.014084507042254</v>
       </c>
     </row>
     <row r="91">
@@ -21451,37 +21451,37 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L91" t="n">
         <v>17</v>
       </c>
       <c r="M91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N91" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O91" t="n">
         <v>11</v>
       </c>
       <c r="P91" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Q91" t="n">
+        <v>28</v>
+      </c>
+      <c r="R91" t="n">
         <v>26</v>
-      </c>
-      <c r="R91" t="n">
-        <v>20</v>
       </c>
       <c r="S91" t="n">
         <v>8</v>
       </c>
       <c r="T91" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U91" t="n">
         <v>2</v>
@@ -21517,31 +21517,31 @@
         <v>4</v>
       </c>
       <c r="AT91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AU91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AV91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AW91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AX91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AY91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AZ91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BA91" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="BB91" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="BC91" t="n">
         <v>4</v>
@@ -21577,31 +21577,31 @@
         <v>8</v>
       </c>
       <c r="CB91" t="n">
-        <v>0.425</v>
+        <v>0.3953488372093023</v>
       </c>
       <c r="CC91" t="n">
-        <v>0.325</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CD91" t="n">
-        <v>0.325</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CE91" t="n">
-        <v>0.275</v>
+        <v>0.2558139534883721</v>
       </c>
       <c r="CF91" t="n">
-        <v>0.3</v>
+        <v>0.3255813953488372</v>
       </c>
       <c r="CG91" t="n">
-        <v>0.65</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="CH91" t="n">
-        <v>0.5</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="CI91" t="n">
-        <v>0.2</v>
+        <v>0.186046511627907</v>
       </c>
       <c r="CJ91" t="n">
-        <v>0.1935483870967742</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="CK91" t="n">
         <v>0.5</v>
@@ -21637,13 +21637,13 @@
         <v>0.5</v>
       </c>
       <c r="DJ91" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="DK91" t="n">
-        <v>644</v>
+        <v>740</v>
       </c>
       <c r="DL91" t="n">
-        <v>4.953846153846154</v>
+        <v>5.103448275862069</v>
       </c>
     </row>
   </sheetData>
